--- a/workspaces/btc_daily_14days/roc/roc_3.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_3.xlsx
@@ -575,46 +575,46 @@
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.48613674383359</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.588211086823534</v>
+        <v>3.576311826838584</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.194060311947773</v>
+        <v>3.183444125774287</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.372742114853359</v>
+        <v>-4.359245481531616</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.61262660181887</v>
+        <v>-12.57274849317112</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-16.1689081711737</v>
+        <v>-16.1173245658712</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.4059581021807</v>
+        <v>-12.36628663466801</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.318591195065864</v>
+        <v>-1.314466219579501</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.087795072901578</v>
+        <v>-9.058354232913779</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-13.79650119942961</v>
+        <v>-13.75238131505277</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-21.71638775594305</v>
+        <v>-21.6470066581519</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.261167164637385</v>
+        <v>-6.240901315869252</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.826747012596044</v>
+        <v>-2.817400977792232</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.57669686984844</v>
+        <v>-2.568398571270755</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>28</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.633890063780086</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-21.96753731959073</v>
+        <v>-21.89756443902201</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-22.36799169626886</v>
+        <v>-22.29669840045288</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-22.24316384953311</v>
+        <v>-22.17212541355678</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-15.63775600842498</v>
+        <v>-15.58763589973893</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-18.91982163920339</v>
+        <v>-18.85872015988587</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-19.00939169227593</v>
+        <v>-18.94799506527581</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-19.4818822847671</v>
+        <v>-19.4194003875919</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-12.3912653087773</v>
+        <v>-12.35082819263602</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.071295924429506</v>
+        <v>1.068280280691326</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-9.874673743725758</v>
+        <v>-9.842378004669797</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-24.16717225619994</v>
+        <v>-24.08916013038823</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-10.26648813570344</v>
+        <v>-10.23313683658014</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-10.0182764832583</v>
+        <v>-9.985980988851551</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.881561679790025</v>
+        <v>6.858579067594803</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.145526421568952</v>
+        <v>2.138527809901866</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.502119707216764</v>
+        <v>-4.487565768818854</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.881746833132645</v>
+        <v>1.875791358525312</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.343204306894563</v>
+        <v>1.339131962227214</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-14.00334021237452</v>
+        <v>-13.95723329995033</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.832410190352356</v>
+        <v>-7.806259198472297</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.171739837972787</v>
+        <v>-5.154624525662264</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.290407244150721</v>
+        <v>7.267769318925311</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.440496539346597</v>
+        <v>6.420064134381832</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>12.50207511541221</v>
+        <v>12.46245448044449</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.405897218315459</v>
+        <v>9.376450614502716</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.98698237131692</v>
+        <v>8.958538240213109</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1654519463467068</v>
+        <v>-0.1645524174260231</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>43</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.64609656351201</v>
+        <v>5.62672083196928</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6167862491962381</v>
+        <v>-0.6148829315951758</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.968222421966018</v>
+        <v>5.948808334625781</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.772734808535148</v>
+        <v>3.760482603295635</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>10.21843807156392</v>
+        <v>10.18526296845816</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.189938943473422</v>
+        <v>8.16433400417597</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.778022407948704</v>
+        <v>5.760154708160208</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>9.971031862385253</v>
+        <v>9.938946575030805</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.581954530045856</v>
+        <v>7.557935986175735</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.732121392888047</v>
+        <v>6.710349729188039</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.859766189357416</v>
+        <v>8.83130994895977</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.564201199795711</v>
+        <v>6.543492596728456</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.811971374190314</v>
+        <v>3.799915125634556</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.269370280875606</v>
+        <v>-5.251761719749126</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>45</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.604549431323107</v>
+        <v>-3.593758920229355</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.450920068886795</v>
+        <v>1.446026264304564</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.726289935578059</v>
+        <v>7.700625640258785</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.634684571966687</v>
+        <v>5.615998895736652</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.546147751185799</v>
+        <v>9.514453657009298</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.279252198372006</v>
+        <v>-1.274107455689695</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.086759766109616</v>
+        <v>3.077394370840906</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.07219855577025</v>
+        <v>7.048983835258916</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>9.239406213555021</v>
+        <v>9.209367185270828</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.708033456888629</v>
+        <v>1.702393405596752</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.503035625851588</v>
+        <v>1.498277438423386</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.376234251258296</v>
+        <v>-7.351293158703598</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-10.02848999344743</v>
+        <v>-9.995033507167889</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-12.01040942526692</v>
+        <v>-11.97010797298218</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>67</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.237904963373133</v>
+        <v>1.232712205014529</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.105017707610436</v>
+        <v>4.091050287853449</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.711058596793741</v>
+        <v>3.698162514346961</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9.817162175562281</v>
+        <v>9.783859620071958</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.798562628097869</v>
+        <v>4.78192648578446</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.6136877860541645</v>
+        <v>0.6126114548001738</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.51873347448177</v>
+        <v>3.507642844296775</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.433731245512014</v>
+        <v>-1.428994363973857</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.486659333976853</v>
+        <v>-4.471377502578989</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.339782426287563</v>
+        <v>-5.321868265636176</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.546616540905184</v>
+        <v>-5.527788768929213</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.520565071990482</v>
+        <v>-2.511241452117389</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.439885671612245</v>
+        <v>-4.424266288546022</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.693324632295123</v>
+        <v>-2.68320913384116</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>73</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.548232840758544</v>
+        <v>-4.533770505373901</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.050727514680595</v>
+        <v>-2.044096187967064</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-9.299209463777402</v>
+        <v>-9.267955669378146</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.058364746116141</v>
+        <v>-5.041873240336379</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-8.341266251298386</v>
+        <v>-8.313446268146279</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1837758627582389</v>
+        <v>0.1841344044927737</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.017031129697678</v>
+        <v>-4.002683171061996</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-9.975465585846237</v>
+        <v>-9.941254902238171</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-7.293995671994153</v>
+        <v>-7.26851995437211</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.521095983367708</v>
+        <v>-9.488177849436617</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.355626341974684</v>
+        <v>-8.326467959052081</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-9.697688011901612</v>
+        <v>-9.66340188411143</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-11.49608630910971</v>
+        <v>-11.45568663002413</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-12.62348637791212</v>
+        <v>-12.57893597906968</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>96</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.714895013123595</v>
+        <v>2.704458450993407</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.06169314616790444</v>
+        <v>0.06119378138868825</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.919997733438635</v>
+        <v>5.89912164091038</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.179622380474569</v>
+        <v>9.146761756267672</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.471874207342573</v>
+        <v>4.455874686214166</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.856614334976122</v>
+        <v>6.833506090954302</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.686871764262193</v>
+        <v>4.671245187810769</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.263756654069731</v>
+        <v>5.245902290684413</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.115959514550994</v>
+        <v>3.10596581659388</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.220355896280658</v>
+        <v>1.216978494262044</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.02931788130077706</v>
+        <v>-0.02812762054161055</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.094089166639542</v>
+        <v>2.088446017839026</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.462343808428891</v>
+        <v>-1.455406800362248</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8780405240102382</v>
+        <v>0.8771142492425383</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.091569161331478</v>
+        <v>-1.096195518305286</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.970327106102815</v>
+        <v>1.982769479381552</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.251361137057401</v>
+        <v>6.29023214251481</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.577624856368978</v>
+        <v>3.601720391372552</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7.717594668067726</v>
+        <v>7.765506629845618</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>8.52708901161882</v>
+        <v>8.578012630981817</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9.38135233091689</v>
+        <v>9.437380852470319</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.239058133328392</v>
+        <v>4.264379583332961</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.053557626845453</v>
+        <v>6.088997943154084</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.27469891525535</v>
+        <v>4.299163001642192</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.757690919767725</v>
+        <v>8.808811908638461</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.171917212104745</v>
+        <v>3.18841052887354</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.818316954651443</v>
+        <v>1.825938196469615</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.818041343903303</v>
+        <v>5.849598525971622</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>186</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.719244771822879</v>
+        <v>-5.700141220726174</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.795139274973266</v>
+        <v>-6.771675689513856</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.812564193918817</v>
+        <v>-1.80743061096635</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.084281893832916</v>
+        <v>2.075095902751201</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.775491248312406</v>
+        <v>4.757129401184969</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.458130751242066</v>
+        <v>3.445466531053142</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.163614361772673</v>
+        <v>-4.149434517174278</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.632946117707014</v>
+        <v>-4.616832866236152</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.079381559859293</v>
+        <v>-3.068418004124695</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.854828840533308</v>
+        <v>-2.844349359989693</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.138992049441697</v>
+        <v>-4.124155532443112</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.488977703223739</v>
+        <v>-2.478898393604346</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.911941137385931</v>
+        <v>-2.899823048767672</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.662101319405764</v>
+        <v>-2.651111557209553</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.906561679790016</v>
+        <v>3.925611559105278</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.496028216218647</v>
+        <v>3.51197437747895</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.502518960134033</v>
+        <v>3.520912667468252</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.570492879050313</v>
+        <v>-1.574915115494605</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.695060283000444</v>
+        <v>-4.71443347670828</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.596586528213052</v>
+        <v>-3.612492112924137</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.081535666630344</v>
+        <v>-4.10175846217566</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.545469951710764</v>
+        <v>-2.558747639346372</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.809468945752492</v>
+        <v>-3.828965658077884</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.852976977579402</v>
+        <v>-1.863343235463674</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.063172247595993</v>
+        <v>-4.084380511307934</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.832245884169787</v>
+        <v>-4.858305265189983</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.846061861823443</v>
+        <v>-2.863365004815535</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.367743787259855</v>
+        <v>-2.382294352908474</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2843394575678033</v>
+        <v>0.2845386192169315</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.06169078331898703</v>
+        <v>0.06172482339889029</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.489071597624218</v>
+        <v>3.490412965608442</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.620895422011102</v>
+        <v>3.622284043027612</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.734121378241383</v>
+        <v>2.735154140541596</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.117048642786095</v>
+        <v>5.118758745663833</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.790145476454988</v>
+        <v>2.790932206178375</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5862174540295584</v>
+        <v>0.586278839292369</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8734177653837207</v>
+        <v>0.8735357300782454</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.068349487562713</v>
+        <v>1.068554512436094</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.212298760366679</v>
+        <v>1.212486938075585</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1457135165926502</v>
+        <v>-0.1460745169791267</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2178815126349534</v>
+        <v>-0.218280718342001</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3800310353005543</v>
+        <v>0.379872669683408</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>359</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7099042981744859</v>
+        <v>0.7059859389431722</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.737997271533821</v>
+        <v>-1.731937025740393</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.575559550774514</v>
+        <v>-1.57344456267856</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6086974556688176</v>
+        <v>-0.6101505627988999</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.8692396008910919</v>
+        <v>-0.8686753214701781</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5439546840341904</v>
+        <v>0.5398803062274027</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.247070978596881</v>
+        <v>3.23599252628766</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.617018121346106</v>
+        <v>3.60538840489582</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.71966752455527</v>
+        <v>2.711616757509773</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.310185504702631</v>
+        <v>1.306857188301549</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.8506590079788623</v>
+        <v>-0.8455012538697773</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.299515529958569</v>
+        <v>0.302245155788313</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1227589828606384</v>
+        <v>-0.1183127469153717</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.269176196315016</v>
+        <v>-1.261349074806219</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.567512394284101</v>
+        <v>-1.565914662928684</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.096373430518227</v>
+        <v>-1.09438009608931</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.808240714995641</v>
+        <v>-3.803737866709987</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.627382912784221</v>
+        <v>-2.624970784963622</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.774331015902384</v>
+        <v>-1.772650136116951</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.245670061052181</v>
+        <v>-1.244905215522408</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.8662373246697044</v>
+        <v>-0.8653243055737647</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6376795492139777</v>
+        <v>-0.6368191820404832</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.23497309747804</v>
+        <v>-0.2343631020850196</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6212987743294036</v>
+        <v>-0.6199462691187776</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.584013435302843</v>
+        <v>3.579683462763136</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.619383146079912</v>
+        <v>3.615583801888796</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.502335739734498</v>
+        <v>2.500459428953405</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.217312158698618</v>
+        <v>3.214217884199535</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.772284474056129</v>
+        <v>-1.778410131237152</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.08923545952716</v>
+        <v>-1.095768923861812</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6335205505846062</v>
+        <v>-0.6349416403439605</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.657407052479996</v>
+        <v>1.667557693618058</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.844088029901279</v>
+        <v>1.853832645393872</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.821899718638853</v>
+        <v>3.840779911155757</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5.903414607832573</v>
+        <v>5.928994223500631</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.442645287423034</v>
+        <v>5.465487475543576</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5.867234132933774</v>
+        <v>5.890993141530942</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.505284550825131</v>
+        <v>5.526701572354135</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>5.303550912387955</v>
+        <v>5.32506957971006</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.85953944886468</v>
+        <v>4.877286608478279</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.820967820703103</v>
+        <v>4.836936904052138</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.139750990784286</v>
+        <v>3.149612231485811</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.1542570336602651</v>
+        <v>-0.1542332859483579</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.450470847135144</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.055674915784699</v>
+        <v>1.05552208776777</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.445650898976183</v>
+        <v>-1.445639408147848</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2296861491360787</v>
+        <v>-0.2297842042046057</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6525511102170185</v>
+        <v>0.6522588601495372</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8602150537634472</v>
+        <v>0.8599093977295738</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9115389356436836</v>
+        <v>-0.9115888444886195</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.142241771180366</v>
+        <v>-2.142124930627872</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.5226745136594531</v>
+        <v>0.522510200765268</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.439456815423441</v>
+        <v>-1.439412602312409</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.112140264805696</v>
+        <v>-1.11205432937183</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6526329481023581</v>
+        <v>-0.6525435444223007</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.7702648974768778</v>
+        <v>0.770198315713202</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.737330910559209</v>
+        <v>1.738980264577911</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.181935010097348</v>
+        <v>-2.18481711963117</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.49988063977078</v>
+        <v>-4.503852721411796</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.754242891778709</v>
+        <v>-4.757684383224124</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.138817953004725</v>
+        <v>-4.141712401845489</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.149068322981329</v>
+        <v>-6.152827698475321</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-7.387648194099803</v>
+        <v>-7.392718474052494</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.777908515958181</v>
+        <v>-4.781265395013641</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.917726474611825</v>
+        <v>-2.919731218936917</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.844110310500746</v>
+        <v>-1.84476122949534</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.593541765623634</v>
+        <v>-3.596167920503206</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.116549452698031</v>
+        <v>-4.120467015203914</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.764459072182682</v>
+        <v>-3.768520853948033</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.286623475774086</v>
+        <v>-4.291000293872486</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.24468210130442</v>
+        <v>-2.249793276820249</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.353768152079617</v>
+        <v>-4.368973150531836</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-4.748636858676349</v>
+        <v>-4.762336955353049</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.60843347731258</v>
+        <v>-6.624635504387093</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.659292503330015</v>
+        <v>-4.670172468984866</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-7.844437630291061</v>
+        <v>-7.86126358015801</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.436634034130385</v>
+        <v>-6.450768381070723</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.913767681668133</v>
+        <v>-4.925149281248139</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.972489989275928</v>
+        <v>-6.989791860535739</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.544949798200321</v>
+        <v>-8.564801527166836</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.262722939928068</v>
+        <v>-6.278402296101419</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.726898536163141</v>
+        <v>-5.744019138755931</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.149917731188602</v>
+        <v>-4.164273749700868</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-7.391971635837955</v>
+        <v>-7.414552417424545</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.3505811773529</v>
+        <v>-3.39098455281988</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.9621547903171219</v>
+        <v>-1.005106126399127</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.928452068342253</v>
+        <v>-1.969877725879698</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-6.941056078591892</v>
+        <v>-7.032449644604121</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-8.622334436521207</v>
+        <v>-8.726940223838135</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-10.6106067845198</v>
+        <v>-10.7335052252492</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-10.69534050179215</v>
+        <v>-10.82094953892052</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.591095329145041</v>
+        <v>-2.625744495685034</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-5.187306482932954</v>
+        <v>-5.26015978773286</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-6.606177476143337</v>
+        <v>-6.69103343269186</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.337324572415007</v>
+        <v>-5.411350272980037</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.432368979279758</v>
+        <v>-2.486793705229978</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.987422985893573</v>
+        <v>-4.063117680336696</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-4.876529922880366</v>
+        <v>-4.969465712222288</v>
       </c>
     </row>
     <row r="25">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.1283</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4091~4104</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4091</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2029899771300521</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.1188</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4065</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.1883868243786821</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.1093</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4037~4050</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4037</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2218333819383673</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.09979</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4005~4018</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4005</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2784059658048008</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.09029</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3962~3975</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3962</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.3424949239835655</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.08079</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3917~3930</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3917</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.3051431548155676</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.07129</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3850~3863</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3850</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.3319058325061235</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.06179</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3777~3790</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3777</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.2506942568854313</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.05229</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3681~3694</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3681</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.3277642541569179</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.04279</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3575~3587</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3575</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.3049799984926622</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.03329</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3389~3401</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3389</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.008874956493421848</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.02379</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3141~3151</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3141</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.3195252767317172</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.01429</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2854~2863</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2854</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.3802703146214341</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.004789</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2495~2504</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2495</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.5365693106253175</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.004711</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2064~2072</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2064</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.3216236483953026</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.01421</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1651~1656</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1651</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.04279356384799371</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.02371</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1310~1314</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1310</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.09408070566522042</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.03321</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1051~1054</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1051</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.3112751323541829</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.04271</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>851~853</t>
-        </is>
+      <c r="B24" t="n">
+        <v>851</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.1443108005403104</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.05221</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>678~678</t>
-        </is>
+      <c r="B25" t="n">
+        <v>678</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.046384688639591</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.06171</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>529~529</t>
-        </is>
+      <c r="B26" t="n">
+        <v>529</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.8146902242134644</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.07121</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>431~431</t>
-        </is>
+      <c r="B27" t="n">
+        <v>431</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.4067936983515139</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.08071</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>353~353</t>
-        </is>
+      <c r="B28" t="n">
+        <v>353</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.3687924278587005</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.09021</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>287~287</t>
-        </is>
+      <c r="B29" t="n">
+        <v>287</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.4682341536576189</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.09971</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>235~235</t>
-        </is>
+      <c r="B30" t="n">
+        <v>235</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.855140447869552</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.1092</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>190~190</t>
-        </is>
+      <c r="B31" t="n">
+        <v>190</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.1187</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>157~157</t>
-        </is>
+      <c r="B32" t="n">
+        <v>157</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-2.174966982630359</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.1282</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>124~124</t>
-        </is>
+      <c r="B33" t="n">
+        <v>124</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-4.106341546016424</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.1377</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>104~104</t>
-        </is>
+      <c r="B34" t="n">
+        <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.1472</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.1283</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10.60179977502812</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.1188</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>110~110</t>
-        </is>
+      <c r="B7" t="n">
+        <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>7.506561679790025</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.1093</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>138~138</t>
-        </is>
+      <c r="B8" t="n">
+        <v>138</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>6.926851534862486</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.09979</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>170~170</t>
-        </is>
+      <c r="B9" t="n">
+        <v>170</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6.91832638567238</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.09029</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>213~213</t>
-        </is>
+      <c r="B10" t="n">
+        <v>213</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>6.661491257254809</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.08079</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>258~258</t>
-        </is>
+      <c r="B11" t="n">
+        <v>258</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>4.870902765061345</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.07129</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>325~325</t>
-        </is>
+      <c r="B12" t="n">
+        <v>325</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>4.121946295174638</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.06179</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>398~398</t>
-        </is>
+      <c r="B13" t="n">
+        <v>398</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>2.531687307930724</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.05229</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>494~494</t>
-        </is>
+      <c r="B14" t="n">
+        <v>494</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.567290424729293</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.04279</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>600~601</t>
-        </is>
+      <c r="B15" t="n">
+        <v>600</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.915879483450588</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.03329</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>786~787</t>
-        </is>
+      <c r="B16" t="n">
+        <v>786</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.1113901423059076</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.02379</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1034~1037</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1034</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.026330242952994</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.01429</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1321~1325</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1321</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.865052245827755</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.004789</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1680~1684</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1680</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.8319773567496469</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.004711</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2111~2116</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2111</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.342100432152975</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.01421</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2524~2532</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2524</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.005286661442205798</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.02371</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2865~2874</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2865</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.02301382473329028</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.03321</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3124~3134</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3124</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.1230262617938536</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.04271</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3324~3335</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3324</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.01967520176920345</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.05221</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3497~3510</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3497</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.1857460125176615</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.06171</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3646~3659</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3646</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.102074559619652</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.07121</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3744~3757</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3744</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.03136751903883095</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.08071</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3822~3835</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3822</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.04893456114596262</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.09021</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3888~3901</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3888</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.01971363423202632</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.09971</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3940~3953</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3940</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.1248262889476308</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.1092</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3985~3998</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3985</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.132874836368309</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.1187</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4018~4031</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4018</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.09897051134547041</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.1282</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4051~4064</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4051</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1394356955380545</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.1377</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4071~4084</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4071</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.07757049467738852</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.1472</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4091~4104</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4091</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.1381406271584424</v>

--- a/workspaces/btc_daily_14days/roc/roc_3.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_3.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-3 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-3 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -572,49 +572,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.48613674383359</v>
+        <v>-0.627706611894844</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.576311826838584</v>
+        <v>5.15152243120837</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.183444125774287</v>
+        <v>4.759138296545892</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.359245481531616</v>
+        <v>-2.498991352058077</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.57274849317112</v>
+        <v>-10.42763543994057</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-16.1173245658712</v>
+        <v>-17.52601132148128</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.36628663466801</v>
+        <v>-10.22016439687783</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.314466219579501</v>
+        <v>-3.292667754090438</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.058354232913779</v>
+        <v>-7.053320105342124</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-13.75238131505277</v>
+        <v>-11.60433803701142</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-21.6470066581519</v>
+        <v>-19.21369296588802</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.240901315869252</v>
+        <v>-4.37651461492262</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.817400977792232</v>
+        <v>-1.094867046821804</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.568398571270755</v>
+        <v>-0.8694264975655202</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.633890063780086</v>
+        <v>3.064129691275618</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-21.89756443902201</v>
+        <v>-24.39052416595158</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-22.29669840045288</v>
+        <v>-24.79017259675622</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-22.17212541355678</v>
+        <v>-24.66623933986762</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-15.58763589973893</v>
+        <v>-17.81826473998895</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-18.85872015988587</v>
+        <v>-17.52555065944888</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-18.94799506527581</v>
+        <v>-21.3118115500875</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-19.4194003875919</v>
+        <v>-18.08543772560871</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-12.35082819263602</v>
+        <v>-14.45144843683507</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.068280280691326</v>
+        <v>-0.5040694619869583</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-9.842378004669797</v>
+        <v>-11.81159479190208</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-24.08916013038823</v>
+        <v>-26.587706325969</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-10.23313683658014</v>
+        <v>-12.20322325657881</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-9.985980988851551</v>
+        <v>-11.98053760867831</v>
       </c>
     </row>
     <row r="8">
@@ -679,306 +679,306 @@
         <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.858579067594803</v>
+        <v>6.871065338020266</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.138527809901866</v>
+        <v>2.151399342029151</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.487565768818854</v>
+        <v>-4.474598559081436</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.875791358525312</v>
+        <v>1.888738172091898</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.339131962227214</v>
+        <v>1.352213008935955</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-13.95723329995033</v>
+        <v>-13.94422449478731</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.806259198472297</v>
+        <v>-7.793220147357303</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.154624525662264</v>
+        <v>-5.141465928693954</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.267769318925311</v>
+        <v>7.280953111143248</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.420064134381832</v>
+        <v>6.433456960759287</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>12.46245448044449</v>
+        <v>12.47590358568685</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.376450614502716</v>
+        <v>9.389897048897801</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.958538240213109</v>
+        <v>8.972091319333984</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1645524174260231</v>
+        <v>-0.1749820531213331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.09504</t>
+          <t>X ≈ -0.09503</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>43</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.62672083196928</v>
+        <v>5.639205515792398</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6148829315951758</v>
+        <v>-0.6020141888966037</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.948808334625781</v>
+        <v>5.961782023492773</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.760482603295635</v>
+        <v>3.773430025715875</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>10.18526296845816</v>
+        <v>10.19834852580377</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.16433400417597</v>
+        <v>8.177353278626583</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.760154708160208</v>
+        <v>5.773199215729562</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>9.938946575030805</v>
+        <v>9.952110469814308</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.557935986175735</v>
+        <v>7.571119629700171</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.710349729188039</v>
+        <v>6.723742426876186</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.83130994895977</v>
+        <v>8.844758249731257</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.543492596728456</v>
+        <v>6.556938581343154</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.799915125634556</v>
+        <v>3.81346783060097</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.251761719749126</v>
+        <v>-5.262191355449389</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.08554</t>
+          <t>X ≈ -0.08553</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>45</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.593758920229355</v>
+        <v>-3.581282752189665</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.446026264304564</v>
+        <v>1.458895683946487</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.700625640258785</v>
+        <v>7.713599926144305</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.615998895736652</v>
+        <v>5.628946867411258</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.514453657009298</v>
+        <v>9.527538387503036</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.274107455689695</v>
+        <v>-1.261093530603262</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.077394370840906</v>
+        <v>3.090437224427802</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.048983835258916</v>
+        <v>7.062146302881722</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>9.209367185270828</v>
+        <v>9.222551080437356</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.702393405596752</v>
+        <v>1.715784558813972</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.498277438423386</v>
+        <v>1.511724142622029</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.351293158703598</v>
+        <v>-7.337849107201201</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-9.995033507167889</v>
+        <v>-9.981481770564045</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-11.97010797298218</v>
+        <v>-11.98053760867831</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.07604</t>
+          <t>X ≈ -0.07603</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>67</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.232712205014529</v>
+        <v>1.245191172649605</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.091050287853449</v>
+        <v>4.103920704639556</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.698162514346961</v>
+        <v>3.711133050215849</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9.783859620071958</v>
+        <v>9.79680959967893</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.78192648578446</v>
+        <v>4.795007759019832</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.6126114548001738</v>
+        <v>0.6256255311112753</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.507642844296775</v>
+        <v>3.520685259340233</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.428994363973857</v>
+        <v>-1.415835779526141</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.471377502578989</v>
+        <v>-4.458198559075726</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.321868265636176</v>
+        <v>-5.308479398432553</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.527788768929213</v>
+        <v>-5.514343784745861</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.511241452117389</v>
+        <v>-2.497797016465249</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.424266288546022</v>
+        <v>-4.410714321052133</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.68320913384116</v>
+        <v>-2.693638769540662</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.06654</t>
+          <t>X ≈ -0.06653</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>73</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.533770505373901</v>
+        <v>-4.521298322275285</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.044096187967064</v>
+        <v>-2.031232243270047</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-9.267955669378146</v>
+        <v>-9.254996345167051</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.041873240336379</v>
+        <v>-5.028934450252137</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-8.313446268146279</v>
+        <v>-8.300374213731885</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1841344044927737</v>
+        <v>0.1971471818621779</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.002683171061996</v>
+        <v>-3.989645256732288</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-9.941254902238171</v>
+        <v>-9.928100742413235</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-7.26851995437211</v>
+        <v>-7.255342779858168</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.488177849436617</v>
+        <v>-9.474790804831507</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.326467959052081</v>
+        <v>-8.313024061172833</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-9.66340188411143</v>
+        <v>-9.649958755289965</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-11.45568663002413</v>
+        <v>-11.4421353180528</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-12.57893597906968</v>
+        <v>-12.58936561476659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.05704</t>
+          <t>X ≈ -0.05703</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>96</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.704458450993407</v>
+        <v>2.716935080880432</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.06119378138868825</v>
+        <v>0.07405740962995111</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.89912164091038</v>
+        <v>5.912090721548978</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.146761756267672</v>
+        <v>9.159708981789407</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.455874686214166</v>
+        <v>4.468953185449564</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.833506090954302</v>
+        <v>6.846521402469051</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.671245187810769</v>
+        <v>4.684286179039489</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.245902290684413</v>
+        <v>5.259061735884188</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.10596581659388</v>
+        <v>3.119145702714206</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.216978494262044</v>
+        <v>1.230367739578007</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.02812762054161055</v>
+        <v>-0.01468258554383794</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.088446017839026</v>
+        <v>2.101890393930596</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.455406800362248</v>
+        <v>-1.441855006733498</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8771142492425383</v>
+        <v>0.8666846135439101</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>106</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.096195518305286</v>
+        <v>-1.083588422221325</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.982769479381552</v>
+        <v>1.9957737546424</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.29023214251481</v>
+        <v>6.303341693443976</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.601720391372552</v>
+        <v>3.614803204779669</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7.765506629845618</v>
+        <v>7.778728850800341</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>8.578012630981817</v>
+        <v>8.078217508106263</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9.437380852470319</v>
+        <v>9.450423156730423</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.264379583332961</v>
+        <v>4.277537482568171</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.088997943154084</v>
+        <v>6.102177991515028</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.299163001642192</v>
+        <v>4.312552330501177</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.808811908638461</v>
+        <v>8.8222583193932</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.18841052887354</v>
+        <v>3.201854643944813</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.825938196469615</v>
+        <v>1.839489998109912</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.849598525971622</v>
+        <v>5.839168890273257</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>186</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.700141220726174</v>
+        <v>-5.687675852534987</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.771675689513856</v>
+        <v>-6.758820858807326</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.80743061096635</v>
+        <v>-1.79446914434439</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.075095902751201</v>
+        <v>2.088037298779547</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.757129401184969</v>
+        <v>4.770208020519952</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.445466531053142</v>
+        <v>3.459564779029954</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.149434517174278</v>
+        <v>-4.136402070738477</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.616832866236152</v>
+        <v>-4.603681405028233</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.068418004124695</v>
+        <v>-3.055243333904471</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.844349359989693</v>
+        <v>-2.830963759158159</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.124155532443112</v>
+        <v>-4.110713251476128</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.478898393604346</v>
+        <v>-2.46545592923659</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.899823048767672</v>
+        <v>-2.886272014862257</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.651111557209553</v>
+        <v>-2.661541192907585</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.925611559105278</v>
+        <v>3.712294816072657</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.51197437747895</v>
+        <v>3.510629693104008</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.520912667468252</v>
+        <v>3.517480040295247</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.574915115494605</v>
+        <v>-1.557955861544379</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.71443347670828</v>
+        <v>-4.902391037118711</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.612492112924137</v>
+        <v>-3.586256138801062</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.10175846217566</v>
+        <v>-4.070632557897177</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.558747639346372</v>
+        <v>-2.533716456912813</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.828965658077884</v>
+        <v>-3.798346256388854</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.863343235463674</v>
+        <v>-1.840682777000247</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.084380511307934</v>
+        <v>-4.051960058654494</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.858305265189983</v>
+        <v>-4.821542796757285</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.863365004815535</v>
+        <v>-2.834329208330658</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.382294352908474</v>
+        <v>-2.208114583243237</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>287</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2845386192169315</v>
+        <v>0.2970609088925542</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.06172482339889029</v>
+        <v>0.07460423002486039</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.490412965608442</v>
+        <v>3.502010197708799</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.622284043027612</v>
+        <v>3.633808641459503</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.735154140541596</v>
+        <v>2.748264944916535</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.118758745663833</v>
+        <v>5.131801641958198</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.790932206178375</v>
+        <v>2.612438973090164</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.586278839292369</v>
+        <v>0.5993577094298175</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8735357300782454</v>
+        <v>0.8865783380927112</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.068554512436094</v>
+        <v>1.081716906276654</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.212486938075585</v>
+        <v>1.225725449023891</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1460745169791267</v>
+        <v>-0.132251593681751</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.218280718342001</v>
+        <v>-0.204306999900119</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.379872669683408</v>
+        <v>0.3694430339852559</v>
       </c>
     </row>
     <row r="18">
@@ -1199,98 +1199,98 @@
         <v>359</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7059859389431722</v>
+        <v>0.7185082286187949</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.731937025740393</v>
+        <v>-1.718424134756887</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.57344456267856</v>
+        <v>-1.560262944538508</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6101505627988999</v>
+        <v>-0.5973846023047855</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.8686753214701781</v>
+        <v>-0.8555645170952388</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5398803062274027</v>
+        <v>0.5529232025217681</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.23599252628766</v>
+        <v>3.249058780588136</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.60538840489582</v>
+        <v>3.617233731865987</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.711616757509773</v>
+        <v>2.723883788878332</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.306857188301549</v>
+        <v>1.319861475411912</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.8455012538697773</v>
+        <v>-0.8314954672900825</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.302245155788313</v>
+        <v>0.3159844228036874</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1183127469153717</v>
+        <v>-0.1042709803168549</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.261349074806219</v>
+        <v>-1.271778710504371</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -3.9e-05</t>
+          <t>X ≈ -3.85e-05</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.565914662928684</v>
+        <v>-1.553392373253061</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.09438009608931</v>
+        <v>-1.080884096127754</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.803737866709987</v>
+        <v>-3.789352834705056</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.624970784963622</v>
+        <v>-2.735308495270303</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.772650136116951</v>
+        <v>-1.759539331742012</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.244905215522408</v>
+        <v>-1.231862319228043</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.8653243055737647</v>
+        <v>-0.8522580512732887</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6368191820404832</v>
+        <v>-0.6234342325824187</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2343631020850196</v>
+        <v>-0.2210279552662016</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6199462691187776</v>
+        <v>-0.6061633846057433</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.579683462763136</v>
+        <v>3.59175800824481</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.615583801888796</v>
+        <v>3.627829058355651</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.500459428953405</v>
+        <v>2.513418845343281</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.214217884199535</v>
+        <v>3.203788248501382</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>413</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.778410131237152</v>
+        <v>-1.765887841561529</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.095768923861812</v>
+        <v>-1.2144628552862</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6349416403439605</v>
+        <v>-0.7527327951979572</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.667557693618058</v>
+        <v>1.680536836016522</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.853832645393872</v>
+        <v>1.866943449768812</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.840779911155757</v>
+        <v>3.853822807450122</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5.928994223500631</v>
+        <v>5.942060477801107</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.465487475543576</v>
+        <v>5.475371990989984</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5.890993141530942</v>
+        <v>5.900777762538617</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.526701572354135</v>
+        <v>5.5370437754409</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>5.32506957971006</v>
+        <v>5.335464006021567</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.877286608478279</v>
+        <v>4.888234041532733</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.836936904052138</v>
+        <v>4.710842720877856</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.149612231485811</v>
+        <v>3.139182595787659</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>341</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.1542332859483579</v>
+        <v>-0.1417109962727352</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.450470847135144</v>
+        <v>1.463380656711195</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.05552208776777</v>
+        <v>1.068529219185372</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.445639408147848</v>
+        <v>-1.432660265749384</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2297842042046057</v>
+        <v>-0.2166733998296664</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6522588601495372</v>
+        <v>0.6653017564439025</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8599093977295738</v>
+        <v>0.8729756520300498</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9115888444886195</v>
+        <v>-1.055810495329098</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.142124930627872</v>
+        <v>-2.128287872969473</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.522510200765268</v>
+        <v>0.5348007587897428</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.439412602312409</v>
+        <v>-1.425726629673562</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.11205432937183</v>
+        <v>-1.09808398328699</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6525435444223007</v>
+        <v>-0.6389874980706978</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.770198315713202</v>
+        <v>0.7597686800150498</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>259</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.738980264577911</v>
+        <v>1.751502554253534</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.18481711963117</v>
+        <v>-2.171907310055119</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.503852721411796</v>
+        <v>-4.490845589994194</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.757684383224124</v>
+        <v>-4.74470524082566</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.141712401845489</v>
+        <v>-4.128601597470549</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.152827698475321</v>
+        <v>-6.139784802180955</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-7.392718474052494</v>
+        <v>-7.379652219752018</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.781265395013641</v>
+        <v>-4.768084385718403</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.919731218936917</v>
+        <v>-2.904594102315642</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.84476122949534</v>
+        <v>-1.830657931376756</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.596167920503206</v>
+        <v>-3.58009850262772</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.120467015203914</v>
+        <v>-4.323183821371458</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.768520853948033</v>
+        <v>-3.75496480759643</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.291000293872486</v>
+        <v>-4.301429929570638</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>200</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.249793276820249</v>
+        <v>-2.237270987144626</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.368973150531836</v>
+        <v>-4.356063340955785</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-4.762336955353049</v>
+        <v>-4.749329823935447</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.624635504387093</v>
+        <v>-6.611656361988629</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.670172468984866</v>
+        <v>-4.657061664609927</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-7.86126358015801</v>
+        <v>-7.848220683863644</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.450768381070723</v>
+        <v>-6.437702126770247</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.925149281248139</v>
+        <v>-4.911968271952901</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.989791860535739</v>
+        <v>-6.968762730630516</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.564801527166836</v>
+        <v>-8.826063835303131</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.258027706473783</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.744019138755931</v>
+        <v>-5.730566850035821</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.164273749700868</v>
+        <v>-4.150717703349265</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-7.414552417424545</v>
+        <v>-7.424982053122697</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>173</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.39098455281988</v>
+        <v>-3.378462263144257</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.005106126399127</v>
+        <v>-0.9921963168230761</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.969877725879698</v>
+        <v>-1.956870594462096</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.032449644604121</v>
+        <v>-7.019470502205657</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-8.726940223838135</v>
+        <v>-8.713829419463195</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-10.7335052252492</v>
+        <v>-10.72046232895483</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-10.82094953892052</v>
+        <v>-10.80788328462005</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.625744495685034</v>
+        <v>-2.612563486389796</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-5.26015978773286</v>
+        <v>-5.571850842514138</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-6.69103343269186</v>
+        <v>-6.677628305039029</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.411350272980037</v>
+        <v>-5.728973876987503</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.486793705229978</v>
+        <v>-2.473341416509868</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.063117680336696</v>
+        <v>-4.049561633985093</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-4.969465712222288</v>
+        <v>-4.97989534792044</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.868977787172618</v>
+        <v>1.573138023519739</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.941967932597578</v>
+        <v>3.340330308834289</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.8086054719855866</v>
+        <v>-0.4328194542991284</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.034057037364661</v>
+        <v>-3.680972689089181</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.125508324744338</v>
+        <v>0.5104674875448865</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.603895375123855</v>
+        <v>-3.246212536874118</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.332924394409595</v>
+        <v>0.04745548223809237</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.155812491177635</v>
+        <v>-3.797991539926983</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.152315139418548</v>
+        <v>1.546431708955652</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.053514743595883</v>
+        <v>-2.68186546575263</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.915986188718826</v>
+        <v>-1.535215272661475</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.539321152178843</v>
+        <v>-0.1494857689547615</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.053847055668243</v>
+        <v>1.457390404758861</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.316991206736432</v>
+        <v>3.710153082012376</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.608602496116525</v>
+        <v>3.074639525021169</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.099069699478861</v>
+        <v>5.503857472361389</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.663384666351625</v>
+        <v>3.088884067404294</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.834454125489742</v>
+        <v>5.239311231194733</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.316441073682896</v>
+        <v>5.711122688199964</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.593474848133262</v>
+        <v>4.998395707734161</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.569965620656966</v>
+        <v>7.943988378771017</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.021149568814174</v>
+        <v>3.43651569458018</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7.021374172427855</v>
+        <v>6.405836568360442</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.089616334338608</v>
+        <v>1.515513731626626</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.90527117328628</v>
+        <v>2.320913583467387</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.960062493897077</v>
+        <v>3.3653927459236</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.5418247701089882</v>
+        <v>-1.095162147793729</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.748712888697966</v>
+        <v>1.150775522634881</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>78</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.916818090046469</v>
+        <v>3.929340379722092</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.58729575913339</v>
+        <v>3.600205568709441</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6537267936169755</v>
+        <v>-0.6407196621993734</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.040628903093086</v>
+        <v>2.053608045491551</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.343946158132894</v>
+        <v>-2.330835353757955</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7644529383660199</v>
+        <v>-0.7514100420716545</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.131237937689576</v>
+        <v>-2.1181716833891</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.529783791734012</v>
+        <v>2.54296480102925</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.377369940602101</v>
+        <v>-1.364171201647338</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.618658720523783</v>
+        <v>1.632063848176614</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>6.542110524411399</v>
+        <v>6.555567818121617</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>10.42264752791075</v>
+        <v>10.43609981663086</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>10.00239291696571</v>
+        <v>10.01594896331731</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.970062967190756</v>
+        <v>8.959633331492604</v>
       </c>
     </row>
     <row r="28">
@@ -1716,101 +1716,101 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.008589835361491</v>
+        <v>-3.250146799765119</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4404426122803571</v>
+        <v>-0.2459482774442918</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.469577609467791</v>
+        <v>-0.6407196621993734</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.690978553442733</v>
+        <v>1.027967019850529</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.152557338370563</v>
+        <v>0.4896774667548343</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-5.366794657456232</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.180188986640594</v>
+        <v>-3.913043478260867</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.647372385422052</v>
+        <v>-4.380112122047564</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.979555817031915</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.0130429111777417</v>
+        <v>-0.6756284595156217</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.763250780949903</v>
+        <v>-5.495714233160435</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.728867623604515</v>
+        <v>-5.461336080805111</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.1188192042463</v>
+        <v>-2.80456385719544</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.869097871970105</v>
+        <v>-2.578828206969</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.09496</t>
+          <t>X ≈ 0.09495</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>10.96810014132848</v>
+        <v>9.783234912861872</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.433449605287251</v>
+        <v>8.172048819797986</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>14.73088859099846</v>
+        <v>13.43765479353362</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>14.8611417236059</v>
+        <v>15.45467238995212</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>10.47656666237995</v>
+        <v>11.14279793119611</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>14.6201624462494</v>
+        <v>15.21375686649151</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.84312103666943</v>
+        <v>7.58187669590459</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.452860714811003</v>
+        <v>5.228015599287666</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.468783905551774</v>
+        <v>3.280240989934697</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.387889489754563</v>
+        <v>8.090699552095401</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.260059242360121</v>
+        <v>5.999205941005023</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.294442399705609</v>
+        <v>6.033584093360346</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.72034163491444</v>
+        <v>9.387018145707316</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.8931398902677</v>
+        <v>11.49954624876408</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>45</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.8524173027989832</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.67276584460361</v>
+        <v>3.685675654179661</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.055674915784699</v>
+        <v>1.068682047202302</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.036294173829987</v>
+        <v>-1.023315031431522</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.796937611124442</v>
+        <v>-3.783826806749502</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.082437275985662</v>
+        <v>3.095503530286138</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.829190567240275</v>
+        <v>-1.816009557945037</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.890190453422576</v>
+        <v>-1.876991714467813</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.962537860672754</v>
+        <v>-4.949132733019923</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-5.167291184990333</v>
+        <v>-5.153833891280115</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-7.35513024986713</v>
+        <v>-7.34167796114702</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.330940416367525</v>
+        <v>-3.317384370015922</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8589968618690804</v>
+        <v>-0.8694264975672326</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>33</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.008589835361491</v>
+        <v>-3.996067545685868</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-8.650466478628779</v>
+        <v>-8.637556669052728</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-12.07563821552844</v>
+        <v>-12.06263108411084</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.854475992011807</v>
+        <v>-2.841496849613343</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.698011883825117</v>
+        <v>5.711122688200057</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.095455269368315</v>
+        <v>-3.08241237307395</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-12.27109807754969</v>
+        <v>-12.25803182324921</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-9.707978446028157</v>
+        <v>-9.694797436732919</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.352233789001666</v>
+        <v>2.365432527956429</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.502108603973817</v>
+        <v>1.515513731626648</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.327658309959233</v>
+        <v>4.341115603669451</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.362041467304664</v>
+        <v>4.375493756024774</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.221811218939123</v>
+        <v>7.211381583240971</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>33</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.082319255547603</v>
+        <v>5.094841545223225</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.501048672886377</v>
+        <v>6.513958482462428</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>9.136482996592811</v>
+        <v>9.149490128010413</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3494833724060129</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.025756851843802</v>
+        <v>9.038799748138167</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>18.03193222548062</v>
+        <v>18.0449984797811</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>17.56474882669912</v>
+        <v>17.57792983599436</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>17.50374894051682</v>
+        <v>17.51694767947158</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>19.68392678579187</v>
+        <v>19.6973319134447</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.3882643705653</v>
+        <v>10.40172166427551</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.45295055821371</v>
+        <v>13.46640284693382</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>13.03269594726881</v>
+        <v>13.04625199362042</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.25211424924201</v>
+        <v>10.24168461354386</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>20</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-12.49343832020998</v>
+        <v>-12.48091603053435</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>10.89498806682577</v>
+        <v>10.90789787640182</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.5001193602291849</v>
+        <v>0.513126491646787</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-14.69534050179204</v>
+        <v>-14.68227424749156</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-6.27840229610149</v>
+        <v>-6.264945002391272</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.664273749700961</v>
+        <v>-6.650717703349358</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>20</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>12.50656167979002</v>
+        <v>12.51908396946565</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>15.89498806682577</v>
+        <v>15.90789787640182</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>20.50011936022921</v>
+        <v>20.51312649164681</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>25.63037249283668</v>
+        <v>25.64335163523514</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>20.09195127776454</v>
+        <v>20.10506208213948</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>15.38939321548021</v>
+        <v>15.40243611177458</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.304659498207819</v>
+        <v>5.317725752508295</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>19.83747609942639</v>
+        <v>19.85065710872163</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.776476213244088</v>
+        <v>9.789674952198851</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.92635102821616</v>
+        <v>18.93975615586899</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.72159770389858</v>
+        <v>13.7350549976088</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.75598086124405</v>
+        <v>13.76943314996416</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.33572625029911</v>
+        <v>13.34928229665071</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.5854475825754</v>
+        <v>18.57501794687725</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-3 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-3 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4091</v>
+        <v>4092</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2029899771300521</v>
+        <v>-0.203205920911941</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.144495238073084</v>
+        <v>-0.1447337025455511</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.136155627581644</v>
+        <v>-0.1363982463498061</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1389520621499116</v>
+        <v>-0.1391934647161008</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1031706734549971</v>
+        <v>-0.1034236530470949</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01247201518741292</v>
+        <v>0.01219220933551668</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.03867609166811548</v>
+        <v>0.03838932899043357</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02461811585308027</v>
+        <v>-0.02489193959462455</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1475699632440879</v>
+        <v>0.1472536683326098</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.04356714543227724</v>
+        <v>0.04327178086899153</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.04792892031284168</v>
+        <v>0.04763131018511046</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.09607370268060578</v>
+        <v>0.0957643663783827</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1050322131534642</v>
+        <v>0.1047184070831548</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.02641556106476628</v>
+        <v>0.02663085010306077</v>
       </c>
     </row>
     <row r="7">
@@ -2269,46 +2269,46 @@
         <v>4065</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1883868243786821</v>
+        <v>-0.2003863591268029</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1682937580454578</v>
+        <v>-0.1799117875667875</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1573879999278347</v>
+        <v>-0.1689147252325185</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1119587955068866</v>
+        <v>-0.123519530409034</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.02341445615792281</v>
+        <v>-0.03484955261754408</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1156392257919734</v>
+        <v>0.1286821220863388</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1180190266951158</v>
+        <v>0.1065273242176019</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.0163681648821381</v>
+        <v>-0.003187155586900303</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.2064516432195163</v>
+        <v>0.1950803576042546</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1318069141832297</v>
+        <v>0.1206359789213352</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1866911158946536</v>
+        <v>0.1755663053767478</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1366054002162258</v>
+        <v>0.1254695404239214</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1237242827634475</v>
+        <v>0.1126861333452496</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.04301215822115267</v>
+        <v>0.03258252252300053</v>
       </c>
     </row>
     <row r="8">
@@ -2318,361 +2318,361 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4037</v>
+        <v>4038</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2218333819383673</v>
+        <v>-0.2222144753627902</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.01758293836069669</v>
+        <v>-0.01802804952410497</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.003833208940783095</v>
+        <v>-0.00428521494744416</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.04104706659502</v>
+        <v>0.04058483681617275</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.08453654716639392</v>
+        <v>0.08405886988345657</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.247242412019105</v>
+        <v>0.2467267692139785</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2502579156163947</v>
+        <v>0.2497405856356849</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1182082290331152</v>
+        <v>0.1177194232616898</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2935469702950542</v>
+        <v>0.2930140568241342</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1253116815198041</v>
+        <v>0.1248130583924905</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.256251169245111</v>
+        <v>0.2557181997864788</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3046315173470049</v>
+        <v>0.3040866153106521</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1955578501009896</v>
+        <v>0.1950361961307792</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1125716846313765</v>
+        <v>0.112907991453767</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.09979</t>
+          <t>X &gt; -0.09978</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2784059658048008</v>
+        <v>-0.2788757219998956</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.03481029015705417</v>
+        <v>-0.03535747451903148</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.03199187018933003</v>
+        <v>0.03142372839062091</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0263874367968242</v>
+        <v>0.02582175475705384</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07451231413719483</v>
+        <v>0.07392883182811971</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3607363502920222</v>
+        <v>0.3600843429653722</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3146295879386969</v>
+        <v>0.3139879005273016</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1603382285712485</v>
+        <v>0.15972989037666</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2378228466605492</v>
+        <v>0.2371942740637181</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0750165308352706</v>
+        <v>0.07441949751487442</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1587234524015741</v>
+        <v>0.1581031392900201</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.232147569504555</v>
+        <v>0.2315089982675147</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1255415273834899</v>
+        <v>0.1249249220562589</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1147859096665371</v>
+        <v>0.1152076623041012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.09029</t>
+          <t>X &gt; -0.09028</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3962</v>
+        <v>3963</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3424949239835655</v>
+        <v>-0.3430890687637245</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02851470116618771</v>
+        <v>-0.02920904183716999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.03222395716321813</v>
+        <v>-0.03292282893701071</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.01413908823079169</v>
+        <v>-0.01484116617437081</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.03522071921358361</v>
+        <v>-0.03592482621905901</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2760430895355839</v>
+        <v>0.2752641147964425</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2555287347914117</v>
+        <v>0.2547534603169268</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.05420997039412612</v>
+        <v>0.05347897821016545</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1583768938591561</v>
+        <v>0.1576185005859543</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.003002566289787012</v>
+        <v>0.002271910847561287</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.06459896493262107</v>
+        <v>0.06384975302987073</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1636498824347328</v>
+        <v>0.162875772914937</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.08566316677652708</v>
+        <v>0.08490288191812567</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1730296118535364</v>
+        <v>0.1735544091532972</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.08079</t>
+          <t>X &gt; -0.08078</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3917</v>
+        <v>3918</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3051431548155676</v>
+        <v>-0.3058969514196264</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.04545479395306273</v>
+        <v>-0.04630059688062715</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.121061902499946</v>
+        <v>-0.1218951423567773</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.07882027517961632</v>
+        <v>-0.07966262138400282</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1449310452105266</v>
+        <v>-0.1457655216293361</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2938518142062847</v>
+        <v>0.292909876420488</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2231100588602857</v>
+        <v>0.2221843512344819</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.02614867753002414</v>
+        <v>-0.02701873225696261</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.05439564210691117</v>
+        <v>0.05350365472242657</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.01652068818271601</v>
+        <v>-0.01740855601269686</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.04812831614347601</v>
+        <v>0.04722026157207893</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2499844335838901</v>
+        <v>0.2490249866988208</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2014740808248945</v>
+        <v>0.2005198572529139</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3125346389961337</v>
+        <v>0.3131496467241064</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.07129</t>
+          <t>X &gt; -0.07128</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3850</v>
+        <v>3851</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3319058325061235</v>
+        <v>-0.332882904240364</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1174407265455386</v>
+        <v>-0.1185064725497682</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1875263274165064</v>
+        <v>-0.1885824674417833</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.250456522707367</v>
+        <v>-0.2514942596107517</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2306711632823948</v>
+        <v>-0.2317254826273896</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2883045685128351</v>
+        <v>0.2871212633682134</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1659506571397031</v>
+        <v>0.1647967737629017</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.001735518830869864</v>
+        <v>-0.002855984355896624</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.133155850079369</v>
+        <v>0.1319986036511338</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.075806139788547</v>
+        <v>0.07464590943578742</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1451637563252604</v>
+        <v>0.1439807889943765</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2980369360103694</v>
+        <v>0.2968144113189126</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2819739781620072</v>
+        <v>0.2807464711055374</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3646683617961699</v>
+        <v>0.3654619873862046</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.06179</t>
+          <t>X &gt; -0.06178</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3777</v>
+        <v>3778</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2506942568854313</v>
+        <v>-0.2519526963217444</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.08020327653660075</v>
+        <v>-0.08154803388841714</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.01202425117525507</v>
+        <v>-0.01339765720516084</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1578503748686302</v>
+        <v>-0.159182683666657</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.07445125789318041</v>
+        <v>-0.07581988247634541</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2903179182542814</v>
+        <v>0.2888597779129398</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2465199633241681</v>
+        <v>0.2450705345427124</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1903706275786519</v>
+        <v>0.1889234934996367</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2762118028792031</v>
+        <v>0.2747397156141318</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2606541226356285</v>
+        <v>0.2591638766516482</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.30889929120017</v>
+        <v>0.3073903586244029</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4905667305215999</v>
+        <v>0.4890098695408369</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5088337145659168</v>
+        <v>0.50726059778858</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6148359860702399</v>
+        <v>0.6157802549767695</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.05229</t>
+          <t>X &gt; -0.05228</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3681</v>
+        <v>3682</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3277642541569179</v>
+        <v>-0.3293598735654726</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.08389089336920108</v>
+        <v>-0.08560510140002009</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1661861652312808</v>
+        <v>-0.1678916507848456</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4005134459333064</v>
+        <v>-0.4021521567475261</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1926015677639512</v>
+        <v>-0.1943147804994041</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1196724239377431</v>
+        <v>0.1178832662460749</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1311237064508433</v>
+        <v>0.1293278126872792</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05852302104288043</v>
+        <v>0.05673086143311679</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2024121871995987</v>
+        <v>0.2005781255104822</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2357133077276927</v>
+        <v>0.2338418856573838</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3176889091103092</v>
+        <v>0.3157876977444829</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4488942470707826</v>
+        <v>0.4469575799315493</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5600608510595606</v>
+        <v>0.5580794728657565</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6079958031676256</v>
+        <v>0.6092384791966339</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3575</v>
+        <v>3576</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.3049799984926622</v>
+        <v>-0.3070029870560944</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.145168096029785</v>
+        <v>-0.1473014545153788</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3576212255448752</v>
+        <v>-0.3597123259773127</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5191810785918918</v>
+        <v>-0.5212229812223228</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4285622583783848</v>
+        <v>-0.4306522035748443</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1311203206627241</v>
+        <v>-0.1180774243683587</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.144810071864697</v>
+        <v>-0.146968637667463</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.06618209660823737</v>
+        <v>-0.06838253393610216</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.02787286128877753</v>
+        <v>0.02564255901258861</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1152306035165225</v>
+        <v>0.1129405134108836</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.0659241432501716</v>
+        <v>0.06363840079404781</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3676666314425034</v>
+        <v>0.3652967609199678</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5225271451536955</v>
+        <v>0.5200958275425194</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4525804497082646</v>
+        <v>0.4542125777497361</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.008874956493421848</v>
+        <v>-0.01178022806521994</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2185174785904707</v>
+        <v>0.2154544774015221</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2780506897855304</v>
+        <v>-0.280991155412039</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.6615639403593221</v>
+        <v>-0.6643859346383536</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.7131708888530994</v>
+        <v>-0.7160091362242937</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3274157335925381</v>
+        <v>-0.3143728372981727</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.07497751940930186</v>
+        <v>0.07192063034175078</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1835733011936966</v>
+        <v>0.1804568731503693</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1978079751769144</v>
+        <v>0.1946823159691036</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.277662551941475</v>
+        <v>0.2744644646491921</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2958901567287668</v>
+        <v>0.2926736241929362</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5238959305451019</v>
+        <v>0.5206123952471486</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.710357518735691</v>
+        <v>0.7069938861523397</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.6229217637497868</v>
+        <v>0.6251654395026165</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>3141</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3070029870560944</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.04151986968216193</v>
+        <v>-0.04576762661309886</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5780006778781654</v>
+        <v>-0.5821116035913221</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5894496164390546</v>
+        <v>-0.5935489681310102</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3972482139762761</v>
+        <v>-0.3841374096013368</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.06804007549823154</v>
+        <v>-0.05499717920386615</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4047548270925461</v>
+        <v>0.4003178744905753</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.4000952984092194</v>
+        <v>0.3956205659825116</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.5157448936892379</v>
+        <v>0.5112261282954762</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4467072623128487</v>
+        <v>0.442140893547851</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.641737697535234</v>
+        <v>0.6370906210184728</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.9488516441848063</v>
+        <v>0.9441070284241917</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9925234486435883</v>
+        <v>0.9877291457913913</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8602008458673396</v>
+        <v>0.8497712101691874</v>
       </c>
     </row>
     <row r="18">
@@ -2841,98 +2841,98 @@
         <v>2854</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3802703146214341</v>
+        <v>-0.3677480249458114</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.05190221968716457</v>
+        <v>-0.05787229474732669</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9871228627697732</v>
+        <v>-0.9928134105195383</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.012984150519969</v>
+        <v>-1.018654656271323</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7122445264312915</v>
+        <v>-0.6991337220563523</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5896277635408111</v>
+        <v>-0.5765848672464458</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.164799358347743</v>
+        <v>0.177865612648219</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3813725667226535</v>
+        <v>0.3751326331971541</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4797652265400956</v>
+        <v>0.4734804786066888</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3841739193607197</v>
+        <v>0.3778247352951638</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5843428019377939</v>
+        <v>0.5778971397159083</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.058958094168702</v>
+        <v>1.052346315230224</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.114282662352373</v>
+        <v>1.107601035705009</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.908502943472385</v>
+        <v>0.8980733077742329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.004789</t>
+          <t>X &gt; -0.004788</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2495</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.5365693106253175</v>
+        <v>-0.5240470209496948</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.189834251404271</v>
+        <v>0.1810608156989417</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9027583376125463</v>
+        <v>-0.9111643593320409</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.070946979374433</v>
+        <v>-1.079270267242869</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6897360473054661</v>
+        <v>-0.6766252429305268</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.752150167166775</v>
+        <v>-0.7391072708724096</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2771077948748726</v>
+        <v>-0.2640415405743965</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.08252390057361225</v>
+        <v>-0.09136608200208229</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1586290743885499</v>
+        <v>0.1496749521988505</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.2514110762545911</v>
+        <v>0.2422771642723518</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.7900798825129129</v>
+        <v>0.7806915068161615</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.16783983560299</v>
+        <v>1.15829978993208</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.291638073946409</v>
+        <v>1.281974604343027</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.220718123657562</v>
+        <v>1.21028848795941</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2064</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3216236483953026</v>
+        <v>-0.3091013587196798</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.4580011040058736</v>
+        <v>0.4445774130813547</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.2969820890461818</v>
+        <v>-0.3101472891354433</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7464391013662137</v>
+        <v>-0.7334599589677495</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.463604277791049</v>
+        <v>-0.4504934734161097</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.6492541275149932</v>
+        <v>-0.6362112312206278</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.1542776998597404</v>
+        <v>-0.1412114455592643</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.03322283698076234</v>
+        <v>0.01973923432549185</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2406928476734862</v>
+        <v>0.2270843287092461</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4333660257971985</v>
+        <v>0.4194466781126991</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2075609178385633</v>
+        <v>0.1936907015275224</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6567072534958314</v>
+        <v>0.6426180483184325</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.039214622392137</v>
+        <v>1.024827090839572</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.8044398306374134</v>
+        <v>0.7940101949392613</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1651</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.04279356384799371</v>
+        <v>0.05531585352361645</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8466788880818044</v>
+        <v>0.8595886976578555</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2124410262442566</v>
+        <v>-0.1994338948266545</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.350303835665734</v>
+        <v>-1.33732469326727</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.043314422718588</v>
+        <v>-1.030203618343648</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.772442533312102</v>
+        <v>-1.759399637017736</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.676016830294522</v>
+        <v>-1.662950575994046</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.325665894531312</v>
+        <v>-1.344995065191419</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.17273781335809</v>
+        <v>-1.192198159583626</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.8407391109247939</v>
+        <v>-0.8607275200681244</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.072591158086894</v>
+        <v>-1.092531209287756</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3990766796403022</v>
+        <v>-0.4194288355080289</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.0892089880338176</v>
+        <v>0.1027650343854205</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2177916164942317</v>
+        <v>0.2073619807960796</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1310</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.09408070566522042</v>
+        <v>0.1066029953408432</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6895086147709719</v>
+        <v>0.7024184243470231</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.5424986001969998</v>
+        <v>-0.5294914687793977</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.325487476721925</v>
+        <v>-1.312508334323461</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.255080685705813</v>
+        <v>-1.241969881330874</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.403605262449815</v>
+        <v>-2.39056236615545</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.336131978200029</v>
+        <v>-2.323065723899553</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.433452363282889</v>
+        <v>-1.420271353987651</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.9204011668016108</v>
+        <v>-0.9485290051831896</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.19560019129603</v>
+        <v>-1.223990988076174</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.9771055760403939</v>
+        <v>-1.005798660927788</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2134847876109518</v>
+        <v>-0.2427712741396206</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2822911357952975</v>
+        <v>0.2958471821469004</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.07399720089601658</v>
+        <v>0.06356756519786444</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1051</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3112751323541829</v>
+        <v>-0.2987528426785602</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.397834366636019</v>
+        <v>1.41074417621207</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4337056979900851</v>
+        <v>0.4467128294076872</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4796844331595267</v>
+        <v>-0.4667052907610625</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5437223465239143</v>
+        <v>-0.530611542148975</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.479676993248489</v>
+        <v>-1.466634096954124</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.090027408812986</v>
+        <v>-1.07696115451251</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.6084442041789231</v>
+        <v>-0.5952631948836853</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.4277023242677842</v>
+        <v>-0.4664920307233444</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.035626158095624</v>
+        <v>-1.074488858376021</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.331684884112839</v>
+        <v>-0.3714088807181994</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.7493205377425909</v>
+        <v>0.7627728264627009</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.280540712715862</v>
+        <v>1.294096759067465</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.149672130624879</v>
+        <v>1.139242494926727</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>851</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1443108005403104</v>
+        <v>0.1568330902159332</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.753135780776525</v>
+        <v>2.766045590352576</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.65486730864653</v>
+        <v>1.667874440064132</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.9644873814650481</v>
+        <v>0.9774665238635123</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4260661663928786</v>
+        <v>0.4391769707678179</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.02010833857513461</v>
+        <v>0.0331512348695</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1698412098139812</v>
+        <v>0.1829074641144572</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4060575765658996</v>
+        <v>0.4192385858611374</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.114504382258175</v>
+        <v>1.061656194871773</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7338627653053607</v>
+        <v>0.7472678929581917</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.065898526460273</v>
+        <v>1.012050302773126</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.275369815415573</v>
+        <v>2.288822104135683</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.560168083436601</v>
+        <v>2.573724129788204</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.162415855195846</v>
+        <v>3.151986219497694</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>678</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.046384688639591</v>
+        <v>1.058906978315214</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.712097211368544</v>
+        <v>3.725007020944595</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.57976537792829</v>
+        <v>2.592772509345892</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.005003761273258</v>
+        <v>3.017982903671722</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.76156779693855</v>
+        <v>2.774678601313489</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.764024483916749</v>
+        <v>2.777067380211115</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.974276017381932</v>
+        <v>2.987342271682408</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.179658990281844</v>
+        <v>1.192839999577082</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.741077983155591</v>
+        <v>2.754276722110355</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.628415924971321</v>
+        <v>2.641821052624152</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.718647851391204</v>
+        <v>2.732105145101421</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.490494135580299</v>
+        <v>3.503946424300409</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.250180527585243</v>
+        <v>4.263736573936846</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.237364986705195</v>
+        <v>5.226935351007043</v>
       </c>
     </row>
     <row r="26">
@@ -3254,49 +3254,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.8146902242134644</v>
+        <v>0.9153103845599873</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.929014531854122</v>
+        <v>3.832426178288607</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.534145825257532</v>
+        <v>3.437654793533568</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.987650375634409</v>
+        <v>4.888634654103065</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.504049576441261</v>
+        <v>3.406948874592274</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.557635181453705</v>
+        <v>4.459039885359438</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.905793713708839</v>
+        <v>3.808291790244212</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.682466647630548</v>
+        <v>2.586506165325396</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.188574511920841</v>
+        <v>3.091561744651678</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.228808495134871</v>
+        <v>4.128435401152011</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.024055170817292</v>
+        <v>3.923734242891818</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.625546078635324</v>
+        <v>4.524150131096192</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.150471051811401</v>
+        <v>5.04739550419788</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.778264217736087</v>
+        <v>5.650489644990451</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>431</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4067936983515139</v>
+        <v>0.4193159880271367</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.435591315085624</v>
+        <v>3.448501124661675</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.504759731458876</v>
+        <v>3.517766862876478</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.795105671490973</v>
+        <v>4.808084813889437</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.864573087509292</v>
+        <v>2.877683891884232</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.322107832649536</v>
+        <v>4.335150728943901</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.845262746467746</v>
+        <v>2.858329000768222</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.378079347686246</v>
+        <v>2.391260356981483</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.317079461503944</v>
+        <v>2.330278200458707</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.71521413726488</v>
+        <v>4.728619264917711</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.278442251462387</v>
+        <v>4.291899545172605</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.77686253177766</v>
+        <v>4.79031482049777</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.444774974197017</v>
+        <v>6.45833102054862</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.694496306473305</v>
+        <v>6.684066670775152</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>353</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3687924278587005</v>
+        <v>-0.3562701381830777</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.402070219800279</v>
+        <v>3.414980029376331</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.423632108104528</v>
+        <v>4.43663923952213</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.403743597652543</v>
+        <v>5.416722740051007</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.015464025639858</v>
+        <v>4.028574830014797</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.446050439276206</v>
+        <v>5.459093335570572</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.944886127103075</v>
+        <v>3.957952381403551</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.344558252400901</v>
+        <v>2.357739261696139</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.133416723159101</v>
+        <v>3.146615462113864</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.399438846913043</v>
+        <v>5.412843974565874</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.778254927694618</v>
+        <v>3.791712221404836</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.529351966059878</v>
+        <v>3.542804254779988</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.658672425936508</v>
+        <v>5.672228472288111</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.191679877192954</v>
+        <v>6.181250241494801</v>
       </c>
     </row>
     <row r="29">
@@ -3410,101 +3410,101 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.4682341536576189</v>
+        <v>0.2968617472434261</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.0831413769303</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.778865004828482</v>
+        <v>5.582570936091223</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.257550193185111</v>
+        <v>6.407240524124028</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.673832810865555</v>
+        <v>4.827284304361669</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.758731194574246</v>
+        <v>7.902436111774534</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.583405142807194</v>
+        <v>5.73439241917503</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.722493521029179</v>
+        <v>3.878434886499406</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.055221857843392</v>
+        <v>5.206341618865515</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.644121063059359</v>
+        <v>6.786978378091213</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.742503627243529</v>
+        <v>5.887832775386578</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.428454728839839</v>
+        <v>5.574988705519679</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.447224508138824</v>
+        <v>7.585393407761828</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.045377896164254</v>
+        <v>8.158351280210589</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.09971</t>
+          <t>X &gt; 0.0997</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>235</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.855140447869552</v>
+        <v>-1.842618158193929</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.341796577464073</v>
+        <v>3.354706387040125</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.797991700654705</v>
+        <v>3.810998832072308</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.353776748155823</v>
+        <v>4.366755890554288</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.389823618190036</v>
+        <v>3.402934422564975</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.240457045267405</v>
+        <v>6.25349994156177</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.560880354745535</v>
+        <v>3.574061364040773</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.627540043031324</v>
+        <v>5.640738781986087</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.479542517577862</v>
+        <v>6.492947645230693</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.849257278366665</v>
+        <v>5.862714572076882</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.458108520818477</v>
+        <v>5.471560809538587</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.165513484341666</v>
+        <v>7.179069530693269</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.415234816617954</v>
+        <v>7.404805180919801</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>190</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.26340911945735</v>
+        <v>3.276318929033401</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.447487781281801</v>
+        <v>4.460494912699403</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.105062082139447</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.494656373374909</v>
+        <v>7.507699269669274</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.830975287681575</v>
+        <v>5.844041541982051</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.408055160612506</v>
+        <v>7.421253899567269</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.18950892295301</v>
+        <v>9.202914050605841</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.458439809161746</v>
+        <v>8.471897102871964</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.492822966507177</v>
+        <v>8.506275255227287</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.651515723983316</v>
+        <v>9.665071770334919</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.374921266785933</v>
+        <v>9.36449163108778</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>157</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.174966982630359</v>
+        <v>-2.162444692954736</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.76759953179392</v>
+        <v>5.780509341369971</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.920501525834268</v>
+        <v>7.93350865725187</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.413811983282535</v>
+        <v>7.426791125681</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.96456274273266</v>
+        <v>4.977673547107599</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.720603406562972</v>
+        <v>9.733646302857338</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.635869689290693</v>
+        <v>9.648935943591169</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.89480094019072</v>
+        <v>7.907981949485958</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.470743729167651</v>
+        <v>8.483942468122414</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.8053319199359</v>
+        <v>10.81873704758873</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.32669324529985</v>
+        <v>9.340150539010068</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.361076402645281</v>
+        <v>9.374528691365391</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.577764466859612</v>
+        <v>9.591320513211215</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.8274857991359</v>
+        <v>9.817056163437748</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>124</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.106341546016424</v>
+        <v>-4.093819256340801</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.572407421664479</v>
+        <v>5.585317231240531</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.596893553777562</v>
+        <v>7.609900685195164</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.114243460578614</v>
+        <v>6.127222602977078</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.382273858409668</v>
+        <v>6.395384662784608</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.905522247738233</v>
+        <v>9.918565144032598</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.401433691756274</v>
+        <v>7.41449994605675</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.321347067168325</v>
+        <v>5.334528076463563</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.066798793889248</v>
+        <v>6.079997532844011</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.442480060474225</v>
+        <v>8.455885188127056</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>9.044178349059862</v>
+        <v>9.05763564277008</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.272109893502076</v>
+        <v>8.285562182222186</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.658306895460392</v>
+        <v>8.671862941811995</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.71447984063991</v>
+        <v>9.704050204941758</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.548834220671921</v>
+        <v>4.561744030247972</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.961657821767638</v>
+        <v>8.97466495318524</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.130372492836678</v>
+        <v>8.143351635235142</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.553489739302968</v>
+        <v>8.566600543677907</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.69708552317248</v>
+        <v>12.71012841946684</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.65081334436173</v>
+        <v>11.66387959866221</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.337476099426389</v>
+        <v>7.350657108721627</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.238014674782548</v>
+        <v>8.251213413737311</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.23404333590847</v>
+        <v>11.2474484635613</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.99082847312935</v>
+        <v>12.00428576683957</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.06367316893632</v>
+        <v>11.07712545765643</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.60495701952988</v>
+        <v>11.61851306588149</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.81621681334462</v>
+        <v>12.80578717764647</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.214405074514886</v>
+        <v>6.227412205932488</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.806236992050216</v>
+        <v>5.819347796425156</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.16180235535075</v>
+        <v>13.17486860965123</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.361285623235915</v>
+        <v>4.374466632531153</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.402541504406642</v>
+        <v>9.415946632059473</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.57874056104144</v>
+        <v>11.59219785475166</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.19286910744197</v>
+        <v>11.20642515379357</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.44259043971826</v>
+        <v>11.43216080402011</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-3 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-3 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.60179977502812</v>
+        <v>10.61432206470374</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.990226162063863</v>
+        <v>9.003135971639914</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.404881264991083</v>
+        <v>7.417888396408685</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.535134397598583</v>
+        <v>7.548113539997047</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.806236992050216</v>
+        <v>5.819347796425156</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.170809432759725</v>
+        <v>3.183990442054963</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1212680194028835</v>
+        <v>-0.1078628917500524</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3260213437204627</v>
+        <v>-0.3125640500102449</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.672590567327418</v>
+        <v>-2.659138278607308</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.09284517827232</v>
+        <v>-3.079289131920717</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="7">
@@ -3960,49 +3960,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.879444329826015</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.713169885007581</v>
+        <v>8.07006003856398</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.409210269320091</v>
+        <v>6.774387752908034</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.721281583745771</v>
+        <v>5.102811094694601</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.455587641400868</v>
+        <v>1.861818838896205</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.701515875428925</v>
+        <v>-4.147113437775019</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.87715868361029</v>
+        <v>-2.430021995239386</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.110203372153663</v>
+        <v>1.607413865478385</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-6.132614695846819</v>
+        <v>-5.660775498251603</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.34637624451112</v>
+        <v>-2.907090690977853</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.369311387010512</v>
+        <v>-4.913593651039854</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-3.516746411483268</v>
+        <v>-3.077413696882722</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.027910113337249</v>
+        <v>-2.59666364929523</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.05091605378824227</v>
+        <v>0.3317747036340037</v>
       </c>
     </row>
     <row r="8">
@@ -4015,358 +4015,358 @@
         <v>138</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.926851534862486</v>
+        <v>6.939373824538109</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.692089516101134</v>
+        <v>1.704999325677186</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.5725831283451228</v>
+        <v>0.5855902597627249</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.7464391013662137</v>
+        <v>-0.7334599589677495</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.009497997597812</v>
+        <v>-1.996387193222873</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.784519827998089</v>
+        <v>-6.771476931703724</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-6.144615864110953</v>
+        <v>-6.131549609810477</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.263973175935931</v>
+        <v>-2.250792166640693</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.39743683023417</v>
+        <v>-7.384238091279407</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.450460565986731</v>
+        <v>-2.4370554383339</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.693294501074831</v>
+        <v>-7.679842212354721</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.490360706222631</v>
+        <v>-4.476804659871028</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.066726330468086</v>
+        <v>-2.077155966166238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.09979</t>
+          <t>X &lt; -0.09978</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>170</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.91832638567238</v>
+        <v>6.930848675348003</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.777341008002239</v>
+        <v>1.79025081757829</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3822335809472932</v>
+        <v>-0.3692264495296911</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2519804483397934</v>
+        <v>-0.2390013059413292</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.378636957529608</v>
+        <v>-1.365526153154669</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-8.140018549225715</v>
+        <v>-8.12697565293135</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.460046384145052</v>
+        <v>-6.446980129844576</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.809582724103016</v>
+        <v>-2.796401714807779</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.635288492638267</v>
+        <v>-4.622089753683504</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7795313247250135</v>
+        <v>-0.7661261970721824</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.748990531395535</v>
+        <v>-2.735533237685317</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.479313256403039</v>
+        <v>-4.465860967682929</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.958391396759708</v>
+        <v>-1.944835350408106</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.708670064483421</v>
+        <v>-1.719099700181573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.09029</t>
+          <t>X &lt; -0.09028</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>213</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.661491257254809</v>
+        <v>6.674013546930432</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.294049099689616</v>
+        <v>1.306958909265667</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.899180393093026</v>
+        <v>0.9121875245106281</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5599499576254132</v>
+        <v>0.5729291000238774</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.960495878703469</v>
+        <v>0.9736066830784083</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.845348568557391</v>
+        <v>-4.832305672263026</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.991115149679437</v>
+        <v>-3.978048895378961</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.232946435784875</v>
+        <v>-0.2197654264896372</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.171880594267648</v>
+        <v>-2.158681855312885</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7338627653053607</v>
+        <v>0.7472678929581917</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.409857695162458</v>
+        <v>-0.3964004014522402</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.253408810117492</v>
+        <v>-2.239956521397382</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.7957291487619287</v>
+        <v>-0.7821731024103258</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.423942088786106</v>
+        <v>-2.434371724484258</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.08079</t>
+          <t>X &lt; -0.08078</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>258</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.870902765061345</v>
+        <v>4.883425054736968</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.32134465597305</v>
+        <v>1.334254465549101</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.089266647050884</v>
+        <v>2.102273778468486</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.44432598120877</v>
+        <v>1.457305123607235</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.456292363035828</v>
+        <v>2.469403167410768</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.223009885295028</v>
+        <v>-4.209966989000662</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.757356005668079</v>
+        <v>-2.744289751367603</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.039026487023285</v>
+        <v>1.052207496318523</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1847640968334332</v>
+        <v>-0.17156535787867</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9030952142626703</v>
+        <v>0.9165003419155013</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.07685190850452273</v>
+        <v>-0.06339461479430497</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.143243944957533</v>
+        <v>-3.129791656237423</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.400707858228024</v>
+        <v>-2.387151811876421</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.088971022075761</v>
+        <v>-4.099400657773913</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.07129</t>
+          <t>X &lt; -0.07128</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>325</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.121946295174638</v>
+        <v>4.134468584850261</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.894988066825775</v>
+        <v>1.907897876401826</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.423196283306098</v>
+        <v>2.4362034147237</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.168834031298218</v>
+        <v>3.181813173696682</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.938105123918355</v>
+        <v>2.951215928293294</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.225991399904444</v>
+        <v>-3.212948503610079</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.464571271022884</v>
+        <v>-1.451505016722408</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5297837917340829</v>
+        <v>0.5429648010293207</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.069677632909759</v>
+        <v>-1.056478893954996</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3813412794761462</v>
+        <v>-0.3679361518233151</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.201479219178339</v>
+        <v>-1.188021925468121</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.013249907986761</v>
+        <v>-2.999797619266651</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.818119903547043</v>
+        <v>-2.80456385719544</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.799167802039982</v>
+        <v>-3.809597437738134</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.06179</t>
+          <t>X &lt; -0.06178</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>398</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.531687307930724</v>
+        <v>2.544209597606347</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.171369976373505</v>
+        <v>1.184279785949556</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2739887069628537</v>
+        <v>0.2869958383804558</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.660523246605528</v>
+        <v>1.673502389003993</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.870845750126314</v>
+        <v>0.8839565545012533</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.60055653326355</v>
+        <v>-2.587513636969184</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.931521406314729</v>
+        <v>-1.918455152014253</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.393679679468086</v>
+        <v>-1.380498670172848</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.208448409871487</v>
+        <v>-2.195249670916724</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.053548469271284</v>
+        <v>-2.040143341618453</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.509558074995894</v>
+        <v>-2.496100781285676</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.233968887499707</v>
+        <v>-4.220516598779597</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.40296721703757</v>
+        <v>-4.389411170685968</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-5.409527291796458</v>
+        <v>-5.41995692749461</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.05229</t>
+          <t>X &lt; -0.05228</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>494</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.567290424729293</v>
+        <v>2.579812714404916</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9557168117650363</v>
+        <v>0.9686266213410875</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.370564704358735</v>
+        <v>1.383571835776337</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.120251035346797</v>
+        <v>3.133230177745261</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.569684071286773</v>
+        <v>1.582794875661712</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7644529383659844</v>
+        <v>-0.751410042071619</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.6467575058406894</v>
+        <v>-0.6336912515402133</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1017951556343419</v>
+        <v>-0.08861414633910414</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.174940790804492</v>
+        <v>-1.161742051849728</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.417778526439704</v>
+        <v>-1.404373398786873</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.027390150352431</v>
+        <v>-2.013932856642214</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.005152741994856</v>
+        <v>-2.991700453274746</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.830265652534891</v>
+        <v>-3.816709606183288</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.187831769651318</v>
+        <v>-4.19826140534947</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>600</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.915879483450588</v>
+        <v>1.928401773126211</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.136252625893981</v>
+        <v>1.149162435470032</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.238888079031177</v>
+        <v>2.251895210448779</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.201087967046334</v>
+        <v>3.214067109444798</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.662666751974164</v>
+        <v>2.675777556349104</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.889393215480176</v>
+        <v>0.8100900219242817</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.137992831541226</v>
+        <v>1.151059085841702</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6708094327597252</v>
+        <v>0.683990442054963</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1098095465774236</v>
+        <v>0.1230082855321868</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.4069823051171753</v>
+        <v>-0.3935771774643442</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1117356294347545</v>
+        <v>-0.0982783357245367</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.910685805422652</v>
+        <v>-1.897233516702542</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.830940416367554</v>
+        <v>-2.817384370015951</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.414552417424602</v>
+        <v>-2.424982053122754</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>786</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1113901423059076</v>
+        <v>0.1239124319815303</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.7377946523610177</v>
+        <v>-0.7248848427849666</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.281567898983944</v>
+        <v>1.294575030401546</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.936598668186107</v>
+        <v>2.949577810584572</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.16056627141127</v>
+        <v>3.173677075786209</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.496263444487802</v>
+        <v>1.438014256628406</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1151878300363904</v>
+        <v>-0.1021215757359144</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5823712288178911</v>
+        <v>-0.5691902195226533</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6433711150001926</v>
+        <v>-0.6301723760454294</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9845904476108132</v>
+        <v>-0.9711853199579821</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.062117308824064</v>
+        <v>-1.048660015113846</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.04554585631324</v>
+        <v>-2.03209356759313</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.84747985657112</v>
+        <v>-2.833923810219517</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.470532061190504</v>
+        <v>-2.480961696888656</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.026330242952994</v>
+        <v>0.9872920619511945</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2826447688508438</v>
+        <v>0.2955545784268949</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.816416370836698</v>
+        <v>1.829423502254301</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.850237488015082</v>
+        <v>1.863216630413547</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.269557455370688</v>
+        <v>1.228495061888722</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2686202686202677</v>
+        <v>0.2286909380293594</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.072152095995001</v>
+        <v>-1.059085841694525</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.056243707336897</v>
+        <v>-1.043062698041659</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.407098665982964</v>
+        <v>-1.393899927028201</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.194421918643741</v>
+        <v>-1.18101679099091</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.785648672913013</v>
+        <v>-1.772191379202795</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.717449090446813</v>
+        <v>-2.703996801726703</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.847848628927942</v>
+        <v>-2.834292582576339</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.449368665006801</v>
+        <v>-2.415320217373967</v>
       </c>
     </row>
     <row r="18">
@@ -4532,101 +4532,101 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.865052245827755</v>
+        <v>0.8373343465395564</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2346107083352038</v>
+        <v>0.247520517911255</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.179364643248043</v>
+        <v>2.192371774665645</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.234146077742338</v>
+        <v>2.247125220140802</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.58741955571012</v>
+        <v>1.557892270818698</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.322877720393244</v>
+        <v>1.293674782469402</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2324055547421864</v>
+        <v>-0.2605055400086371</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.699588953523687</v>
+        <v>-0.6864079442284492</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9118747701144585</v>
+        <v>-0.8986760311596953</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7029984422830893</v>
+        <v>-0.6895933146302582</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.134680662213377</v>
+        <v>-1.121223368503159</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.15929901772725</v>
+        <v>-2.14584672900714</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.276981767855204</v>
+        <v>-2.263425721503602</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.834688677833384</v>
+        <v>-1.810761175664361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.004789</t>
+          <t>X &lt; -0.004788</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8319773567496469</v>
+        <v>0.812852515459717</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1857720281861077</v>
+        <v>-0.1728622186100566</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.378979217711368</v>
+        <v>1.39198634912897</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.627997195924564</v>
+        <v>1.640976338323028</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.063430778655771</v>
+        <v>1.043304362424479</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.156337329629991</v>
+        <v>1.136244786759676</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5098944773869505</v>
+        <v>0.4901395456118109</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2211762778915869</v>
+        <v>0.2343572871868247</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.137265607100943</v>
+        <v>-0.1240668681461798</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2735299949843082</v>
+        <v>-0.2601248673314771</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.073167316922358</v>
+        <v>-1.059710023212141</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.633668157197391</v>
+        <v>-1.620215868477281</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.81596916909411</v>
+        <v>-1.802413122742507</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.712171465043646</v>
+        <v>-1.695654272040059</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.342100432152975</v>
+        <v>0.3296649803300795</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3715525758963523</v>
+        <v>-0.3586427663203011</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3205352392461904</v>
+        <v>0.3335423706637926</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7603961334986167</v>
+        <v>0.7473213894884552</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4845719021732151</v>
+        <v>0.4714923421867283</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.666250763989396</v>
+        <v>0.6531456671198441</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2289019224503122</v>
+        <v>0.2159746876716397</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.04580943275972515</v>
+        <v>0.05899044205496295</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1572359079680368</v>
+        <v>-0.1440371690132736</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3444823051171753</v>
+        <v>-0.3310771774643442</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.1230992657983876</v>
+        <v>-0.1096419720881698</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5622009569378079</v>
+        <v>-0.5487486682176979</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9351070830342252</v>
+        <v>-0.9215510366826223</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7063572492578629</v>
+        <v>-0.6958153864560899</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.005286661442205798</v>
+        <v>-0.01348610554422436</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4898400643476819</v>
+        <v>-0.4981052831558443</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1641509807825301</v>
+        <v>0.1555603122710423</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9091388036314569</v>
+        <v>0.9002686312825787</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.7090398853594451</v>
+        <v>0.7001589583751056</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.186781422840681</v>
+        <v>1.177752567470733</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.163725214755793</v>
+        <v>1.154686575618769</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9340715071856991</v>
+        <v>0.9472525164809369</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.8334833391348226</v>
+        <v>0.8466820780895858</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6167706640039654</v>
+        <v>0.6301757916567965</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7683118765034891</v>
+        <v>0.7817691702137068</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.3276356514261138</v>
+        <v>0.3410879401462239</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.008993577031780831</v>
+        <v>0.0001136505699506074</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.07540820189370123</v>
+        <v>-0.06854640955840097</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.02301382473329028</v>
+        <v>-0.02874211749087863</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2588580870203856</v>
+        <v>-0.2646838911695113</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2703143463015962</v>
+        <v>0.2642577133662414</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6286309393709857</v>
+        <v>0.6224602703326383</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5971777586007434</v>
+        <v>0.5909554990673485</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.123098339216668</v>
+        <v>1.11672182606025</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.127532580495192</v>
+        <v>1.121141576837402</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7146996780800379</v>
+        <v>0.7083976944956873</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4793014661216617</v>
+        <v>0.4925002050764249</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6058069054397421</v>
+        <v>0.6192120330925732</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5056925765877978</v>
+        <v>0.5191498702980155</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.1563994172258703</v>
+        <v>0.1698517059459803</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.06971687600933052</v>
+        <v>-0.07590082159134681</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.02523815849162503</v>
+        <v>0.03000747932664893</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1230262617938536</v>
+        <v>0.1187649901993026</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4184495329188849</v>
+        <v>-0.4226700878611069</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1256788517759304</v>
+        <v>-0.1300270353241757</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1816340706073589</v>
+        <v>0.17719582425174</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.2037723640264915</v>
+        <v>0.1992811814687343</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.518827539545363</v>
+        <v>0.5142571980365176</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4197490122743872</v>
+        <v>0.4152009842117863</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2580069596758321</v>
+        <v>0.2534704079543602</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1970070734935305</v>
+        <v>0.2102058124482937</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4022064807265551</v>
+        <v>0.4156116083793862</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.165473623310163</v>
+        <v>0.1789309170203808</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.1979538796389022</v>
+        <v>-0.2024248609089199</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3762737497008857</v>
+        <v>-0.3807241013019436</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3326061946333141</v>
+        <v>-0.3289820531227505</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.01967520176920345</v>
+        <v>-0.02288245739286765</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6557017952018285</v>
+        <v>-0.6588187652773456</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4044710988167211</v>
+        <v>-0.407689345185851</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.2279708444982589</v>
+        <v>-0.2312358235107297</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.08967586123278437</v>
+        <v>-0.09301714955323348</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.01401784010479901</v>
+        <v>0.01066186980516193</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.005770943086226055</v>
+        <v>0.00241043719304912</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.05435082365053745</v>
+        <v>-0.05772378644208942</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2355430175251385</v>
+        <v>-0.2223442785703753</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1373700418168937</v>
+        <v>-0.1407726902848552</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2218949321098407</v>
+        <v>-0.2084376383996229</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5314514899285712</v>
+        <v>-0.5347447881182319</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6041233737610341</v>
+        <v>-0.6074224538002824</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.7587160756676852</v>
+        <v>-0.7558091207919304</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1857460125176615</v>
+        <v>-0.1881219547724555</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6709851449154698</v>
+        <v>-0.6732987047947603</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4804963752326259</v>
+        <v>-0.48288376768636</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5629551376166972</v>
+        <v>-0.5653142712642918</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5155786708949321</v>
+        <v>-0.5179775528762391</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5164555719663326</v>
+        <v>-0.5188416976949526</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5286738351254456</v>
+        <v>-0.5310616939966266</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1810794244103207</v>
+        <v>-0.1835894666208375</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4833753001768102</v>
+        <v>-0.4858032093769395</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4609668809526539</v>
+        <v>-0.463442016603878</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.4784022961014145</v>
+        <v>-0.4808833057331086</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6281288843975972</v>
+        <v>-0.6305668500358692</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7751942757157551</v>
+        <v>-0.7776111014630303</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.9670259661806782</v>
+        <v>-0.9647190456899324</v>
       </c>
     </row>
     <row r="26">
@@ -4951,46 +4951,46 @@
         <v>3646</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.102074559619652</v>
+        <v>-0.1168821414936332</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5238200250277032</v>
+        <v>-0.510910215451652</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4938647797762954</v>
+        <v>-0.4808576483586933</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7044196297016185</v>
+        <v>-0.6914404873031543</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4894440710726968</v>
+        <v>-0.4763332666977576</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6423528162658627</v>
+        <v>-0.6293099199714973</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5206895299881182</v>
+        <v>-0.5076232756876422</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3432467921398725</v>
+        <v>-0.3300657828446347</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4166215681856613</v>
+        <v>-0.4034228292308981</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.5667996567153466</v>
+        <v>-0.5533945290625155</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5371033100778533</v>
+        <v>-0.5236460163676355</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6245015948963371</v>
+        <v>-0.611049306176227</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.7004678818643058</v>
+        <v>-0.6869118355127029</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.7919523077153272</v>
+        <v>-0.774954625805151</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3744</v>
+        <v>3745</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.03136751903883095</v>
+        <v>-0.03280533335500024</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3510183229505941</v>
+        <v>-0.3524162039814627</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3853666584126287</v>
+        <v>-0.3867670120805968</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.5337191427520196</v>
+        <v>-0.5350771264159917</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3117257805888087</v>
+        <v>-0.3131584825915041</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4794767205539472</v>
+        <v>-0.4808572535332161</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.283183743594293</v>
+        <v>-0.2846196632698934</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2291905672402734</v>
+        <v>-0.2306545415049825</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2221900977721774</v>
+        <v>-0.2236583811344843</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4973416078564128</v>
+        <v>-0.4987607819810975</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.4470705640491062</v>
+        <v>-0.4485095701606738</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.5045637196422632</v>
+        <v>-0.5059871863048855</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.696316473332395</v>
+        <v>-0.6977011523615673</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7254498533220328</v>
+        <v>-0.7240474736834983</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3822</v>
+        <v>3823</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.04893456114596262</v>
+        <v>0.04775967332383146</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2708961272274379</v>
+        <v>-0.2720238967402864</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3908276786437668</v>
+        <v>-0.3919334979202489</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4813185301278295</v>
+        <v>-0.4823984299879172</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3531022330681708</v>
+        <v>-0.3542281057519929</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4852804137626521</v>
+        <v>-0.4863657676303177</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3208301857827038</v>
+        <v>-0.321960931564746</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1729732213677551</v>
+        <v>-0.1741535468020103</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2457343955878954</v>
+        <v>-0.2468976705806654</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4542030752861947</v>
+        <v>-0.4553313800599312</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3045460869510919</v>
+        <v>-0.3057186563378878</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2816760425216742</v>
+        <v>-0.282854431735224</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.4780325778463208</v>
+        <v>-0.4791695861944731</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5275822447401453</v>
+        <v>-0.5264730287963033</v>
       </c>
     </row>
     <row r="29">
@@ -5107,98 +5107,98 @@
         <v>3888</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.01971363423202632</v>
+        <v>-0.007191344556403578</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2588580870203856</v>
+        <v>-0.2715893030853564</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.409088128870593</v>
+        <v>-0.3960809974529909</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4445377175276164</v>
+        <v>-0.4572127567607467</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3276022249298691</v>
+        <v>-0.3401521852457208</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5551653060804043</v>
+        <v>-0.567789760915403</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3692814517279288</v>
+        <v>-0.3818891383773888</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2318613427924063</v>
+        <v>-0.2443608676522828</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3301253793580159</v>
+        <v>-0.3426137711507522</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.4467219419791135</v>
+        <v>-0.4590105450559818</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3801756191546133</v>
+        <v>-0.3924186595487456</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3571296786017442</v>
+        <v>-0.3693843307556719</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.5058782752858733</v>
+        <v>-0.5180357799756692</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5503548865603989</v>
+        <v>-0.560784522258551</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.09971</t>
+          <t>X &lt; 0.0997</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3940</v>
+        <v>3941</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1248262889476308</v>
+        <v>0.1240409750296365</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1576435121216022</v>
+        <v>-0.158380899211636</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2098274886698306</v>
+        <v>-0.2105577188795351</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2430452286823055</v>
+        <v>-0.2437655502875131</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1853341109414899</v>
+        <v>-0.1860771583668779</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3552876355836645</v>
+        <v>-0.3559837413528371</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2742612010573779</v>
+        <v>-0.2749794146648838</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1701265361539441</v>
+        <v>-0.1708782345770885</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2932322785176424</v>
+        <v>-0.2939540391848325</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.343425848051595</v>
+        <v>-0.3441475196696686</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.3057926080466444</v>
+        <v>-0.3065271524926203</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2825782458082458</v>
+        <v>-0.2833185619303791</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3841418034943445</v>
+        <v>-0.3848628073574005</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3993239910286661</v>
+        <v>-0.3985928118134368</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3985</v>
+        <v>3986</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.132874836368309</v>
+        <v>0.1322372577877289</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.114519063521989</v>
+        <v>-0.1151136293510575</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1955763354665123</v>
+        <v>-0.1961554698243262</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2519804483397934</v>
+        <v>-0.2525442606607555</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2260256876836593</v>
+        <v>-0.226602498586459</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.340634332729195</v>
+        <v>-0.3411793113601647</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2364226661207738</v>
+        <v>-0.2369950088239676</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1888330962639131</v>
+        <v>-0.1894230515990145</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.3112430850015215</v>
+        <v>-0.311803374035172</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.3955341560405401</v>
+        <v>-0.3960834431285036</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.3606490363220871</v>
+        <v>-0.3612097303932131</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3624038891949084</v>
+        <v>-0.3629640416106028</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4174097256165936</v>
+        <v>-0.4179612448591925</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4045147762702683</v>
+        <v>-0.403908294969213</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4018</v>
+        <v>4019</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.09897051134547041</v>
+        <v>0.09844904883073013</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1844163996754702</v>
+        <v>-0.184883071253843</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.292881384372464</v>
+        <v>-0.2933251212564372</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2733017872030388</v>
+        <v>-0.273749382387102</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.1774800607008515</v>
+        <v>-0.177956785785085</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3632148322098416</v>
+        <v>-0.3636428551983997</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3350920545871361</v>
+        <v>-0.335528097466792</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2668976580288813</v>
+        <v>-0.2673553136386175</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2893950271237955</v>
+        <v>-0.2898479106242107</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3799642378206372</v>
+        <v>-0.3804029293907689</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3221725025177307</v>
+        <v>-0.3226277472942414</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3236211288057405</v>
+        <v>-0.3240759273798162</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.331852749452068</v>
+        <v>-0.3323097431502831</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3418794457969199</v>
+        <v>-0.3413791668326382</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4051</v>
+        <v>4052</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1394356955380545</v>
+        <v>0.1390101687276371</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1301165356846923</v>
+        <v>-0.1304879503698331</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2162765038771752</v>
+        <v>-0.2166298460347349</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1711542247205742</v>
+        <v>-0.1715178871676173</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1789846828266235</v>
+        <v>-0.1793506240905458</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2868817290874617</v>
+        <v>-0.2872190606392593</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1857298561538698</v>
+        <v>-0.1860929220420147</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1218534544311396</v>
+        <v>-0.1222359420422876</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1446283232450654</v>
+        <v>-0.1450058464208226</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2166822640156525</v>
+        <v>-0.2170485778588116</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2349883839159261</v>
+        <v>-0.2353519074466917</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2114506709543633</v>
+        <v>-0.2118199334103252</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2230101761569543</v>
+        <v>-0.2233799288612559</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2555793243611646</v>
+        <v>-0.2551893581573026</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4071</v>
+        <v>4072</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.07757049467738852</v>
+        <v>0.07722350434936942</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.07611161478089912</v>
+        <v>-0.07643121272649012</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2127664800451967</v>
+        <v>-0.2130552374739594</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1917299330393334</v>
+        <v>-0.192023181031395</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2021663692943108</v>
+        <v>-0.202460583873787</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3080816558118187</v>
+        <v>-0.3083482019509631</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2568902810956857</v>
+        <v>-0.2571700552876592</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.146580805160319</v>
+        <v>-0.146890708835997</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1695493019669101</v>
+        <v>-0.1698541132904836</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2454281128881348</v>
+        <v>-0.2457198009514201</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2646565916340649</v>
+        <v>-0.2649450023911939</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.241072907476827</v>
+        <v>-0.2413670464030844</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2546470306439161</v>
+        <v>-0.2549406348494117</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2858371140593405</v>
+        <v>-0.2854928586237406</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4091</v>
+        <v>4092</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1381406271584424</v>
+        <v>0.1378415821331274</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.001739224515262094</v>
+        <v>0.001465127863809812</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1117772755582394</v>
+        <v>-0.1120258359184163</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.06579917261077384</v>
+        <v>-0.06605840864589396</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1031706734549971</v>
+        <v>-0.1034236530470949</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2314899267496386</v>
+        <v>-0.2317102296888791</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.229747529610556</v>
+        <v>-0.229968807140331</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.04902621934343898</v>
+        <v>-0.04929408698359339</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1209847242559121</v>
+        <v>-0.1212354700613361</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1517930499279174</v>
+        <v>-0.1520407191310085</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1963309722128059</v>
+        <v>-0.1965689340151329</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1726778243167075</v>
+        <v>-0.1729215153998283</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1882229188113413</v>
+        <v>-0.1884650769139</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1935795501549862</v>
+        <v>-0.1933104988705594</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/roc/roc_3.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_3.xlsx
@@ -572,101 +572,101 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.627706611894844</v>
+        <v>1.331192451531749</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.15152243120837</v>
+        <v>3.587997644586338</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.759138296545892</v>
+        <v>3.196257914605226</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.498991352058077</v>
+        <v>-4.346846238338721</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-10.42763543994057</v>
+        <v>-12.51132841750195</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-17.52601132148128</v>
+        <v>-19.91912524365566</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-10.22016439687783</v>
+        <v>-12.30539228794269</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.292667754090438</v>
+        <v>-5.092652960722312</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.053320105342124</v>
+        <v>-5.13057953275468</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-11.60433803701142</v>
+        <v>-9.797381991663727</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-19.21369296588802</v>
+        <v>-17.69043458342969</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.37651461492262</v>
+        <v>-2.259555374295651</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.094867046821804</v>
+        <v>1.190015813835245</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.8694264975655202</v>
+        <v>1.439324398749854</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.114</t>
+          <t>X ≈ -0.1139</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.064129691275618</v>
+        <v>3.035060126120449</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-24.39052416595158</v>
+        <v>-24.39190080310603</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-24.79017259675622</v>
+        <v>-24.7905060480517</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-24.66623933986762</v>
+        <v>-24.66689647456077</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-17.81826473998895</v>
+        <v>-17.76993672539349</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-17.52555065944888</v>
+        <v>-17.50173732742537</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-21.3118115500875</v>
+        <v>-21.26398623631674</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-18.08543772560871</v>
+        <v>-18.03633794013735</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.45144843683507</v>
+        <v>-14.37833406044897</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5040694619869583</v>
+        <v>-0.4048249249725586</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-11.81159479190208</v>
+        <v>-11.71178731970461</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-26.587706325969</v>
+        <v>-26.46410857579483</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-12.20322325657881</v>
+        <v>-12.05457980786881</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-11.98053760867831</v>
+        <v>-11.80853884911165</v>
       </c>
     </row>
     <row r="8">
@@ -679,670 +679,670 @@
         <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.871065338020266</v>
+        <v>6.842031764001867</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.151399342029151</v>
+        <v>2.150234100824754</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.474598559081436</v>
+        <v>-4.474785005401131</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.888738172091898</v>
+        <v>1.888257279149428</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.352213008935955</v>
+        <v>1.400653910007897</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-13.94422449478731</v>
+        <v>-13.92039513686952</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.793220147357303</v>
+        <v>-7.745334487579115</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.141465928693954</v>
+        <v>-5.092316383345739</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.280953111143248</v>
+        <v>7.354138848431383</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.433456960759287</v>
+        <v>6.532718914767642</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>12.47590358568685</v>
+        <v>12.57575899213762</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>9.389897048897801</v>
+        <v>9.513541975881445</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.972091319333984</v>
+        <v>9.120748439257277</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1749820531213331</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.09503</t>
+          <t>X ≈ -0.09498</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>43</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.639205515792398</v>
+        <v>5.610165046437146</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6020141888966037</v>
+        <v>-0.6032016935829674</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.961782023492773</v>
+        <v>5.961674275649884</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.773430025715875</v>
+        <v>3.772962760607911</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>10.19834852580377</v>
+        <v>10.2468430805745</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.177353278626583</v>
+        <v>8.201302102915996</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.773199215729562</v>
+        <v>5.82114797890948</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>9.952110469814308</v>
+        <v>10.00132091418524</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.571119629700171</v>
+        <v>7.644305490082665</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.723742426876186</v>
+        <v>6.823003911164179</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.844758249731257</v>
+        <v>8.944605539822561</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.556938581343154</v>
+        <v>6.680578815292556</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.81346783060097</v>
+        <v>3.962120851242013</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.262191355449389</v>
+        <v>-5.090192595881668</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.08553</t>
+          <t>X ≈ -0.08549</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>45</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.581282752189665</v>
+        <v>-3.61040390809967</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.458895683946487</v>
+        <v>1.457725673874357</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.713599926144305</v>
+        <v>7.713507961286957</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.628946867411258</v>
+        <v>5.628494029066999</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.527538387503036</v>
+        <v>9.576028932755641</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.261093530603262</v>
+        <v>-1.237197753887514</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.090437224427802</v>
+        <v>3.13837179091243</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.062146302881722</v>
+        <v>7.111344476382364</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>9.222551080437356</v>
+        <v>9.295741820980076</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.715784558813972</v>
+        <v>1.815030244392169</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.511724142622029</v>
+        <v>1.611554778423418</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.337849107201201</v>
+        <v>-7.214229782466319</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-9.981481770564045</v>
+        <v>-9.832839364301719</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-11.98053760867831</v>
+        <v>-11.80853884911165</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.07603</t>
+          <t>X ≈ -0.076</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>67</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.245191172649605</v>
+        <v>1.216117537947291</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.103920704639556</v>
+        <v>4.102774958915269</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.711133050215849</v>
+        <v>3.711012187413971</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9.79680959967893</v>
+        <v>9.796389902979811</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.795007759019832</v>
+        <v>4.843467088564253</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.6256255311112753</v>
+        <v>0.6495304053487416</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.520685259340233</v>
+        <v>3.568620235986273</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.415835779526141</v>
+        <v>-1.366675712793075</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.458198559075726</v>
+        <v>-4.385059310899038</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.308479398432553</v>
+        <v>-5.209257272206251</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.514343784745861</v>
+        <v>-5.414530877782298</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.497797016465249</v>
+        <v>-2.374173093347373</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.410714321052133</v>
+        <v>-4.262069375174804</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.693638769540662</v>
+        <v>-2.521640009974</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.06653</t>
+          <t>X ≈ -0.0665</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.521298322275285</v>
+        <v>-4.553226586507705</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.031232243270047</v>
+        <v>-2.114184531684394</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-9.254996345167051</v>
+        <v>-10.59871915015138</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.028934450252137</v>
+        <v>-5.076844030476828</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-8.300374213731885</v>
+        <v>-9.618618211278545</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1971471818621779</v>
+        <v>0.09083367555827238</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.989645256732288</v>
+        <v>-4.016761523865831</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-9.928100742413235</v>
+        <v>-9.885611029536776</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-7.255342779858168</v>
+        <v>-7.227445158147709</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.474790804831507</v>
+        <v>-9.413212208353656</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.313024061172833</v>
+        <v>-8.860615296560141</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-9.649958755289965</v>
+        <v>-10.15541167430223</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-11.4421353180528</v>
+        <v>-11.90422037658657</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-12.58936561476659</v>
+        <v>-13.00974005031346</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.05703</t>
+          <t>X ≈ -0.057</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.716935080880432</v>
+        <v>3.267940593608479</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.07405740962995111</v>
+        <v>0.6414071622227056</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.912090721548978</v>
+        <v>6.547915612507964</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.159708981789407</v>
+        <v>9.829048349494641</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.468953185449564</v>
+        <v>5.142355952292476</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.846521402469051</v>
+        <v>7.517952564686667</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.684286179039489</v>
+        <v>5.357426190930425</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.259061735884188</v>
+        <v>5.944739362119336</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.119145702714206</v>
+        <v>3.80646899774343</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.230367739578007</v>
+        <v>1.932474531388372</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.01468258554383794</v>
+        <v>0.6767710229420487</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.101890393930596</v>
+        <v>2.839225627848585</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.441855006733498</v>
+        <v>-0.712224841636143</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8666846135439101</v>
+        <v>1.641753548549175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.04754</t>
+          <t>X ≈ -0.0475</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.083588422221325</v>
+        <v>-1.580026387317197</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.9957737546424</v>
+        <v>1.457495058385639</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.303341693443976</v>
+        <v>6.605233621405176</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.614803204779669</v>
+        <v>3.965198358046493</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7.778728850800341</v>
+        <v>8.098085998535986</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>8.078217508106263</v>
+        <v>8.373206424942111</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9.450423156730423</v>
+        <v>8.314968669456576</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.277537482568171</v>
+        <v>3.228787557445578</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.102177991515028</v>
+        <v>5.042689479186627</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.312552330501177</v>
+        <v>3.295778770447619</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.8222583193932</v>
+        <v>7.71764587011468</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.201854643944813</v>
+        <v>3.150870546844907</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.839489998109912</v>
+        <v>1.830944081103169</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.839168890273257</v>
+        <v>5.784053743481579</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03804</t>
+          <t>X ≈ -0.03801</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.687675852534987</v>
+        <v>-6.526122160380986</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.758820858807326</v>
+        <v>-7.591733255041852</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.79446914434439</v>
+        <v>-2.654138266491941</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.088037298779547</v>
+        <v>0.6797784001483791</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.770208020519952</v>
+        <v>3.388446489159534</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.459564779029954</v>
+        <v>3.128242414543479</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.136402070738477</v>
+        <v>-3.875822267577213</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.603681405028233</v>
+        <v>-3.813804123750437</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.055243333904471</v>
+        <v>-2.249827548908399</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.830963759158159</v>
+        <v>-2.248680797142725</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.110713251476128</v>
+        <v>-3.522506185884772</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.46545592923659</v>
+        <v>-2.629182679344353</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.886272014862257</v>
+        <v>-3.025055696377656</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.661541192907585</v>
+        <v>-2.777047464679086</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.02854</t>
+          <t>X ≈ -0.02851</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>249</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.712294816072657</v>
+        <v>3.894330570728954</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.510629693104008</v>
+        <v>3.511481791348935</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.517480040295247</v>
+        <v>3.51966957877643</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.557955861544379</v>
+        <v>-1.559132605758698</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.902391037118711</v>
+        <v>-4.856576795488778</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.586256138801062</v>
+        <v>-4.184154199325235</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.070632557897177</v>
+        <v>-4.648656290834658</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.533716456912813</v>
+        <v>-3.111071200314186</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.798346256388854</v>
+        <v>-4.353684169520655</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.840682777000247</v>
+        <v>-2.370531323226814</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.051960058654494</v>
+        <v>-4.181457456924861</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.821542796757285</v>
+        <v>-4.926901052582053</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.834329208330658</v>
+        <v>-3.087173652168474</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.208114583243237</v>
+        <v>-2.839328675082285</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.01904</t>
+          <t>X ≈ -0.01902</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>287</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2970609088925542</v>
+        <v>0.4341909285351164</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.07460423002486039</v>
+        <v>0.5807592359622262</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.502010197708799</v>
+        <v>3.666201191370632</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.633808641459503</v>
+        <v>4.146280342927064</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.748264944916535</v>
+        <v>3.306372681812341</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.131801641958198</v>
+        <v>5.509266846712244</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.612438973090164</v>
+        <v>3.01175988833652</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5993577094298175</v>
+        <v>0.8039252880976733</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8865783380927112</v>
+        <v>0.9603369889243965</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.081716906276654</v>
+        <v>1.181705591282324</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.225725449023891</v>
+        <v>1.3260085583237</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.132251593681751</v>
+        <v>-0.008977413344766205</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.204306999900119</v>
+        <v>-0.05566974857142526</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3694430339852559</v>
+        <v>0.5414417935519182</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.009539</t>
+          <t>X ≈ -0.009524</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>359</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7185082286187949</v>
+        <v>0.6903725534280625</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.718424134756887</v>
+        <v>-1.721590662851014</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.560262944538508</v>
+        <v>-1.56100874875527</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5973846023047855</v>
+        <v>-0.5973526665026725</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.8555645170952388</v>
+        <v>-0.8072367240084972</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5529232025217681</v>
+        <v>0.578212154151835</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.249058780588136</v>
+        <v>3.301964850611959</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.617233731865987</v>
+        <v>3.672956812292171</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.723883788878332</v>
+        <v>2.800719131089771</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.319861475411912</v>
+        <v>1.420302901302463</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.8314954672900825</v>
+        <v>-0.7327661326526069</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3159844228036874</v>
+        <v>0.4393291508306376</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1042709803168549</v>
+        <v>0.04435256179008462</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.271778710504371</v>
+        <v>-1.099779950937709</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -3.85e-05</t>
+          <t>X ≈ -3.05e-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.553392373253061</v>
+        <v>-1.590906412183919</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.080884096127754</v>
+        <v>-1.332404221650222</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.789352834705056</v>
+        <v>-3.573965712616804</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.735308495270303</v>
+        <v>-2.51912316374321</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.759539331742012</v>
+        <v>-1.624581675202087</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.231862319228043</v>
+        <v>-1.118937849153326</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.8522580512732887</v>
+        <v>-0.8246655730884243</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6234342325824187</v>
+        <v>-0.7016605665322331</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2210279552662016</v>
+        <v>-0.2757587311651193</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6061633846057433</v>
+        <v>-0.6364044805863927</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.59175800824481</v>
+        <v>3.555827496904065</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.627829058355651</v>
+        <v>3.614148427713857</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.513418845343281</v>
+        <v>2.525131777638776</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.203788248501382</v>
+        <v>3.237757447184599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.009461</t>
+          <t>X ≈ 0.009463</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.765887841561529</v>
+        <v>-1.675060406595342</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.2144628552862</v>
+        <v>-1.101475839748993</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.7527327951979572</v>
+        <v>-0.7720132859623519</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.680536836016522</v>
+        <v>1.529151960332541</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.866943449768812</v>
+        <v>1.649049226262157</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.853822807450122</v>
+        <v>3.609744686002998</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5.942060477801107</v>
+        <v>5.716367752008523</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.475371990989984</v>
+        <v>5.249023152763968</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5.900777762538617</v>
+        <v>5.693396777985484</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.5370437754409</v>
+        <v>5.349053706776452</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>5.335464006021567</v>
+        <v>5.145029554537373</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.888234041532733</v>
+        <v>4.720338218682762</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>4.710842720877856</v>
+        <v>4.5642834227883</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.139182595787659</v>
+        <v>3.024125140178931</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.1417109962727352</v>
+        <v>-0.03217918018605559</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.463380656711195</v>
+        <v>1.593310021571881</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.068529219185372</v>
+        <v>1.202110449135127</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.432660265749384</v>
+        <v>-1.433166248955722</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2166733998296664</v>
+        <v>-0.1680294249953675</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6653017564439025</v>
+        <v>0.689551415460997</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8729756520300498</v>
+        <v>0.9212929870542439</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.055810495329098</v>
+        <v>-1.006528077422693</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.128287872969473</v>
+        <v>-2.213091329834349</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.5348007587897428</v>
+        <v>0.471852019175266</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.425726629673562</v>
+        <v>-1.486674393273113</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.09808398328699</v>
+        <v>-1.136109995089541</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6389874980706978</v>
+        <v>-0.6540749391971872</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.7597686800150498</v>
+        <v>0.7645605660929959</v>
       </c>
     </row>
     <row r="22">
@@ -1404,465 +1404,465 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.751502554253534</v>
+        <v>1.717681658225601</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.171907310055119</v>
+        <v>-2.167457654818669</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.490845589994194</v>
+        <v>-4.487026898357499</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.74470524082566</v>
+        <v>-4.741758241758248</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.128601597470549</v>
+        <v>-4.077161228864014</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.139784802180955</v>
+        <v>-6.11206801773735</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-7.379652219752018</v>
+        <v>-7.326570260809007</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.768084385718403</v>
+        <v>-4.715479944269227</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.904594102315642</v>
+        <v>-2.829375630329189</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.830657931376756</v>
+        <v>-1.730127288067166</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.58009850262772</v>
+        <v>-3.472729274064832</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.323183821371458</v>
+        <v>-4.183793305930706</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.75496480759643</v>
+        <v>-3.809720463263723</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.301429929570638</v>
+        <v>-4.329906370479165</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.03796</t>
+          <t>X ≈ 0.03795</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>200</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.237270987144626</v>
+        <v>-2.504801714436653</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.356063340955785</v>
+        <v>-4.086803502210465</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-4.749329823935447</v>
+        <v>-4.48702689835757</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.611656361988629</v>
+        <v>-6.357142857142833</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.657061664609927</v>
+        <v>-4.346391998094745</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-7.848220683863644</v>
+        <v>-7.573606479275938</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.437702126770247</v>
+        <v>-6.134262568501342</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.911968271952901</v>
+        <v>-4.60009532888462</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.968762730630516</v>
+        <v>-6.637067938021396</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-8.826063835303131</v>
+        <v>-8.460896518836464</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.258027706473783</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.730566850035821</v>
+        <v>-5.606870229007541</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.150717703349265</v>
+        <v>-4.002028155571516</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-7.424982053122697</v>
+        <v>-7.752983293556092</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.04746</t>
+          <t>X ≈ 0.04745</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-3.378462263144257</v>
+        <v>-2.805561990869023</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.9921963168230761</v>
+        <v>-1.246487041265979</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.956870594462096</v>
+        <v>-2.214299625630304</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.019470502205657</v>
+        <v>-7.198051948051983</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-8.713829419463195</v>
+        <v>-8.823664725367536</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-10.72046232895483</v>
+        <v>-10.82360647927582</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-10.80788328462005</v>
+        <v>-10.88426256850128</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.612563486389796</v>
+        <v>-2.827368056157418</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-5.571850842514138</v>
+        <v>-5.705249756203273</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-6.677628305039029</v>
+        <v>-7.097260155200104</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.728973876987503</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.473341416509868</v>
+        <v>-3.265961138098575</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.049561633985093</v>
+        <v>-4.797482701025999</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-4.97989534792044</v>
+        <v>-5.116619657192459</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.05696</t>
+          <t>X ≈ 0.05694</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>148</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.573138023519739</v>
+        <v>1.543102668656019</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.340330308834289</v>
+        <v>3.339984956919707</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4328194542991284</v>
+        <v>-0.4329728443034497</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.680972689089181</v>
+        <v>-3.681467181467184</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.5104674875448865</v>
+        <v>0.5590134073106583</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.246212536874118</v>
+        <v>-3.222255127924505</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.04745548223809237</v>
+        <v>0.09546716122841303</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.797991539926983</v>
+        <v>-3.748743977533266</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.546431708955652</v>
+        <v>1.619688818735348</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.68186546575263</v>
+        <v>-2.582518140458056</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.535215272661475</v>
+        <v>-1.435307236642799</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.1494857689547615</v>
+        <v>-0.02578914792651688</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.457390404758861</v>
+        <v>1.606079952536689</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.710153082012376</v>
+        <v>3.882151841579038</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.06646</t>
+          <t>X ≈ 0.06643</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>99</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.074639525021169</v>
+        <v>3.515302392617635</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.503857472361389</v>
+        <v>5.926875064923408</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.088884067404294</v>
+        <v>3.088730677399973</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.239311231194733</v>
+        <v>5.23881673881673</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.711122688199964</v>
+        <v>5.759668607965736</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.998395707734161</v>
+        <v>5.022353116683774</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.943988378771017</v>
+        <v>7.992000057761338</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.43651569458018</v>
+        <v>3.485763256973897</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.405836568360442</v>
+        <v>6.479093678140138</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.515513731626626</v>
+        <v>1.6148610569212</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.320913583467387</v>
+        <v>2.420821619486063</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.3653927459236</v>
+        <v>3.489089366951845</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.095162147793729</v>
+        <v>-0.9464726000159018</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.150775522634881</v>
+        <v>1.322774282201543</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.07596</t>
+          <t>X ≈ 0.07593</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>78</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.929340379722092</v>
+        <v>3.900144585369461</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.600205568709441</v>
+        <v>3.599018782264785</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6407196621993734</v>
+        <v>-0.6408730522036947</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.053608045491551</v>
+        <v>2.053113553113548</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.330835353757955</v>
+        <v>-2.282289433992183</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7514100420716545</v>
+        <v>-0.7274526331220414</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.1181716833891</v>
+        <v>-2.07016000439878</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.54296480102925</v>
+        <v>2.592212363422966</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.364171201647338</v>
+        <v>-1.290914091867641</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.632063848176614</v>
+        <v>1.731411173471187</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>6.555567818121617</v>
+        <v>6.655475854140292</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>10.43609981663086</v>
+        <v>10.55979643765911</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>10.01594896331731</v>
+        <v>10.16463851109514</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.959633331492604</v>
+        <v>9.131632091059267</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.08546</t>
+          <t>X ≈ 0.08543</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>65</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.250146799765119</v>
+        <v>-3.27934259411775</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2459482774442918</v>
+        <v>-0.2471350638889476</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6407196621993734</v>
+        <v>-0.6408730522036947</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.027967019850529</v>
+        <v>1.027472527472526</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.4896774667548343</v>
+        <v>0.5382233865206061</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.366794657456232</v>
+        <v>-5.342837248506619</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.913043478260867</v>
+        <v>-3.865031799270547</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.380112122047564</v>
+        <v>-4.330864559653847</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.979555817031915</v>
+        <v>-5.906298707252219</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.6756284595156217</v>
+        <v>-0.5762811342210483</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.495714233160435</v>
+        <v>-5.395806197141759</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-5.461336080805111</v>
+        <v>-5.337639459776867</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.80456385719544</v>
+        <v>-2.655874309417612</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.578828206969</v>
+        <v>-2.406829447402338</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.09495</t>
+          <t>X ≈ 0.09492</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>9.783234912861872</v>
+        <v>9.028349713574556</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>8.172048819797986</v>
+        <v>7.445172628418703</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>13.43765479353362</v>
+        <v>12.82066540933477</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>15.45467238995212</v>
+        <v>14.87362637362642</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>11.14279793119611</v>
+        <v>10.53822338652061</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>15.21375686649151</v>
+        <v>14.65716275149337</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.58187669590459</v>
+        <v>6.904198969960284</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.228015599287666</v>
+        <v>4.515289286500014</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.280240989934697</v>
+        <v>4.478316677363104</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.090699552095401</v>
+        <v>9.423718865778952</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.999205941005023</v>
+        <v>7.296501495165934</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.033584093360346</v>
+        <v>7.354668232530827</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.387018145707316</v>
+        <v>10.80566415212085</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>11.49954624876408</v>
+        <v>11.05470901413627</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.1045</t>
+          <t>X ≈ 0.1044</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.8524173027989832</v>
+        <v>1.837714262069532</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.685675654179661</v>
+        <v>4.60236326387021</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.068682047202302</v>
+        <v>2.034712232077268</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.023315031431522</v>
+        <v>-0.009316770186394763</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.783826806749502</v>
+        <v>-2.672478954616523</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>1.948132651158929</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.095503530286138</v>
+        <v>4.061389605411669</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.816009557945037</v>
+        <v>-0.7522692419281896</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.876991714467813</v>
+        <v>-2.963154894543123</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.949132733019923</v>
+        <v>-5.960896518836471</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-5.153833891280115</v>
+        <v>-6.165036966372561</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-7.34167796114702</v>
+        <v>-8.280783272485927</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.317384370015922</v>
+        <v>-4.328115112093165</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8694264975672326</v>
+        <v>0.2687558368786611</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>33</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.996067545685868</v>
+        <v>-4.025263340038499</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-8.637556669052728</v>
+        <v>-8.638743455497384</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-12.06263108411084</v>
+        <v>-12.06278447411516</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.841496849613343</v>
+        <v>-2.841991341991346</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.711122688200057</v>
+        <v>5.759668607965828</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.08241237307395</v>
+        <v>-3.058454964124337</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-12.25803182324921</v>
+        <v>-12.21002014425889</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-9.694797436732919</v>
+        <v>-9.645549874339203</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.365432527956429</v>
+        <v>2.438689637736125</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.515513731626648</v>
+        <v>1.614861056921221</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.341115603669451</v>
+        <v>4.441023639688126</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.375493756024774</v>
+        <v>4.499190377053019</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.211381583240971</v>
+        <v>7.383380342807634</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>33</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.094841545223225</v>
+        <v>5.065645750870594</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.513958482462428</v>
+        <v>6.512771696017772</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>9.149490128010413</v>
+        <v>9.149336738006092</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3494833724060129</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.038799748138167</v>
+        <v>9.062757157087781</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>18.0449984797811</v>
+        <v>18.09301015877142</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>17.57792983599436</v>
+        <v>17.62717739838808</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>17.51694767947158</v>
+        <v>17.59020478925128</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>19.6973319134447</v>
+        <v>19.79667923873927</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>10.40172166427551</v>
+        <v>10.50162970029419</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.46640284693382</v>
+        <v>13.59009946796207</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>13.04625199362042</v>
+        <v>13.19494154139824</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.24168461354386</v>
+        <v>10.41368337311052</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>20</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-12.48091603053435</v>
+        <v>-12.51011182488698</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>10.90789787640182</v>
+        <v>10.90671108995716</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.513126491646787</v>
+        <v>0.5129731016424657</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-14.68227424749156</v>
+        <v>-14.63426256850124</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-6.264945002391272</v>
+        <v>-6.165036966372597</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.650717703349358</v>
+        <v>-6.50202815557153</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>20</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>12.51908396946565</v>
+        <v>12.48988817511302</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>15.90789787640182</v>
+        <v>15.90671108995716</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>20.51312649164681</v>
+        <v>20.51297310164249</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>25.64335163523514</v>
+        <v>25.64285714285714</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>20.10506208213948</v>
+        <v>20.15360800190525</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>15.40243611177458</v>
+        <v>15.42639352072419</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.317725752508295</v>
+        <v>5.365737431498616</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>19.85065710872163</v>
+        <v>19.89990467111534</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.789674952198851</v>
+        <v>9.862932061978547</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>18.93975615586899</v>
+        <v>19.03910348116356</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.7350549976088</v>
+        <v>13.83496303362747</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.76943314996416</v>
+        <v>13.89312977099241</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.34928229665071</v>
+        <v>13.49797184442854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.57501794687725</v>
+        <v>18.74701670644391</v>
       </c>
     </row>
   </sheetData>
@@ -2210,781 +2210,781 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1283</t>
+          <t>X &gt; -0.1282</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4092</v>
+        <v>4102</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.203205920911941</v>
+        <v>-0.1893341821166317</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1447337025455511</v>
+        <v>-0.1555154535528018</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1363982463498061</v>
+        <v>-0.1471290136018908</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1391934647161008</v>
+        <v>-0.1499444135630981</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1034236530470949</v>
+        <v>-0.1151830465014925</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01219220933551668</v>
+        <v>0.0006027664662369148</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.03838932899043357</v>
+        <v>0.02623877002388042</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.02489193959462455</v>
+        <v>-0.036804189644144</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1472536683326098</v>
+        <v>0.1587684388960113</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.04327178086899153</v>
+        <v>0.05469042709634664</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.04763131018511046</v>
+        <v>0.05907996419995243</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.0957643663783827</v>
+        <v>0.1065800633900267</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1047184070831548</v>
+        <v>0.1150812765513791</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.02663085010306077</v>
+        <v>0.03663152848193363</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.1188</t>
+          <t>X &gt; -0.1187</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4065</v>
+        <v>4076</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2003863591268029</v>
+        <v>-0.1990333215854392</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1799117875667875</v>
+        <v>-0.1793945851896055</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1689147252325185</v>
+        <v>-0.1684558193264678</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.123519530409034</v>
+        <v>-0.123173204671005</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.03484955261754408</v>
+        <v>-0.03611048034692033</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1286821220863388</v>
+        <v>0.1276667822324669</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1065273242176019</v>
+        <v>0.1048998121011877</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.003187155586900303</v>
+        <v>-0.00455392761077178</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1950803576042546</v>
+        <v>0.1925081462716136</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1206359789213352</v>
+        <v>0.1175348537125842</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1755663053767478</v>
+        <v>0.1723006163683394</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1254695404239214</v>
+        <v>0.1216731746215913</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1126861333452496</v>
+        <v>0.1082244811712485</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.03258252252300053</v>
+        <v>0.02768402734675135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.1093</t>
+          <t>X &gt; -0.1092</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4038</v>
+        <v>4049</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2222144753627902</v>
+        <v>-0.2205992694955441</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.01802804952410497</v>
+        <v>-0.01793801124943428</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.00428521494744416</v>
+        <v>-0.004268277667890175</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.04058483681617275</v>
+        <v>0.04049202829689591</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.08405886988345657</v>
+        <v>0.08214422664647003</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.2467267692139785</v>
+        <v>0.2452251697258703</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2497405856356849</v>
+        <v>0.2473942362324095</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1177194232616898</v>
+        <v>0.1156876550857504</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2930140568241342</v>
+        <v>0.2896710851655229</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1248130583924905</v>
+        <v>0.1210181123009946</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2557181997864788</v>
+        <v>0.2515474363915473</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3040866153106521</v>
+        <v>0.2989554930363099</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1950361961307792</v>
+        <v>0.1893298691199021</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.112907991453767</v>
+        <v>0.1066116681628486</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.09978</t>
+          <t>X &gt; -0.09973</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4006</v>
+        <v>4017</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2788757219998956</v>
+        <v>-0.2768612045395926</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.03535747451903148</v>
+        <v>-0.03520998226919403</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.03142372839062091</v>
+        <v>0.03134450184106186</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.02582175475705384</v>
+        <v>0.02577246443647851</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07392883182811971</v>
+        <v>0.07164078879046798</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3600843429653722</v>
+        <v>0.3580705393576906</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3139879005273016</v>
+        <v>0.311065463307834</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.15972989037666</v>
+        <v>0.1571753646276477</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2371942740637181</v>
+        <v>0.2333945184678612</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.07441949751487442</v>
+        <v>0.06994158113869986</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1581031392900201</v>
+        <v>0.1533709938264778</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2315089982675147</v>
+        <v>0.2255507712411884</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1249249220562589</v>
+        <v>0.1181809036619939</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1152076623041012</v>
+        <v>0.1074847173973552</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.09028</t>
+          <t>X &gt; -0.09024</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3963</v>
+        <v>3974</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3430890687637245</v>
+        <v>-0.3405607840041185</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02920904183716999</v>
+        <v>-0.02906412328920283</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.03292282893701071</v>
+        <v>-0.03282363612416361</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.01484116617437081</v>
+        <v>-0.01477337923121524</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.03592482621905901</v>
+        <v>-0.03845827979199612</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2752641147964425</v>
+        <v>0.2732041686397721</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2547534603169268</v>
+        <v>0.2514445402653323</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.05347897821016545</v>
+        <v>0.05065843995956243</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1576185005859543</v>
+        <v>0.1532060001539648</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.002271910847561287</v>
+        <v>-0.003128796362830144</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.06384975302987073</v>
+        <v>0.05824691595083209</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.162875772914937</v>
+        <v>0.1557052237086651</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.08490288191812567</v>
+        <v>0.07658819662979965</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1735544091532972</v>
+        <v>0.1637253123825104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.08078</t>
+          <t>X &gt; -0.08074</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3918</v>
+        <v>3929</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3058969514196264</v>
+        <v>-0.3031103028169682</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.04630059688062715</v>
+        <v>-0.04609276693194886</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1218951423567773</v>
+        <v>-0.1215446648550014</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.07966262138400282</v>
+        <v>-0.07940739128857643</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1457655216293361</v>
+        <v>-0.1485758477646684</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.292909876420488</v>
+        <v>0.290503248943601</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2221843512344819</v>
+        <v>0.2183797079214571</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.02701873225696261</v>
+        <v>-0.03020968720740314</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.05350365472242657</v>
+        <v>0.04849383117020523</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.01740855601269686</v>
+        <v>-0.02395271003907595</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.04722026157207893</v>
+        <v>0.04045642121648285</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2490249866988208</v>
+        <v>0.2401152708651679</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2005198572529139</v>
+        <v>0.190083803716071</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3131496467241064</v>
+        <v>0.300847197663046</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.07128</t>
+          <t>X &gt; -0.07125</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3851</v>
+        <v>3862</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.332882904240364</v>
+        <v>-0.3294666635966692</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1185064725497682</v>
+        <v>-0.1180694985818178</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1885824674417833</v>
+        <v>-0.1880338696975841</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2514942596107517</v>
+        <v>-0.2507378984651751</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2317254826273896</v>
+        <v>-0.2351804248578873</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2871212633682134</v>
+        <v>0.2842746576750486</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1647967737629017</v>
+        <v>0.160257979443891</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.002855984355896624</v>
+        <v>-0.007023974179382719</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1319986036511338</v>
+        <v>0.1254094346188452</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.07464590943578742</v>
+        <v>0.06600467102389018</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1439807889943765</v>
+        <v>0.1350923997335514</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2968144113189126</v>
+        <v>0.2854693155058285</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2807464711055374</v>
+        <v>0.2673220903513993</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3654619873862046</v>
+        <v>0.3498131849524526</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.06178</t>
+          <t>X &gt; -0.06175</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3778</v>
+        <v>3788</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2519526963217444</v>
+        <v>-0.2469539301501413</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.08154803388841714</v>
+        <v>-0.07907464313049672</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.01339765720516084</v>
+        <v>0.01534276988890326</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.159182683666657</v>
+        <v>-0.1564581060235497</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.07581988247634541</v>
+        <v>-0.0518714501495765</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2888597779129398</v>
+        <v>0.2880535997755374</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2450705345427124</v>
+        <v>0.2418576212720112</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1889234934996367</v>
+        <v>0.1859579271132361</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2747397156141318</v>
+        <v>0.2690502054384609</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2591638766516482</v>
+        <v>0.2511847262176445</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3073903586244029</v>
+        <v>0.3108269217836366</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4890098695408369</v>
+        <v>0.489435839593952</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.50726059778858</v>
+        <v>0.5050977351648811</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6157802549767695</v>
+        <v>0.6107970654724255</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.05228</t>
+          <t>X &gt; -0.05225</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3682</v>
+        <v>3693</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3293598735654726</v>
+        <v>-0.3373722837263884</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.08560510140002009</v>
+        <v>-0.09760856447048383</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1678916507848456</v>
+        <v>-0.1527033768884678</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4021521567475261</v>
+        <v>-0.4133287026317873</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1943147804994041</v>
+        <v>-0.1854895392998586</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1178832662460749</v>
+        <v>0.1020691963998175</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1293278126872792</v>
+        <v>0.1102629789439433</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05673086143311679</v>
+        <v>0.03781705618835929</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2005781255104822</v>
+        <v>0.178052429844378</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2338418856573838</v>
+        <v>0.2079346499947334</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3157876977444829</v>
+        <v>0.3014132500776867</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4469575799315493</v>
+        <v>0.4289890402751837</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5580794728657565</v>
+        <v>0.5364125591009881</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6092384791966339</v>
+        <v>0.584276386920493</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.04279</t>
+          <t>X &gt; -0.04276</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3576</v>
+        <v>3585</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.3070029870560944</v>
+        <v>-0.2999366789320206</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1473014545153788</v>
+        <v>-0.1444568744477337</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3597123259773127</v>
+        <v>-0.3562897634479398</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5212229812223228</v>
+        <v>-0.5452341203593321</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4306522035748443</v>
+        <v>-0.4350365847911419</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1180774243683587</v>
+        <v>-0.1471031385186166</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.146968637667463</v>
+        <v>-0.1369080711468129</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.06838253393610216</v>
+        <v>-0.05831259907964181</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.02564255901258861</v>
+        <v>0.03150269446670251</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1129405134108836</v>
+        <v>0.114911730884856</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.06363840079404781</v>
+        <v>0.0779953636163242</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3652967609199678</v>
+        <v>0.3469909363115775</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5200958275425194</v>
+        <v>0.4974141199444375</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4542125777497361</v>
+        <v>0.4276303745052701</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03329</t>
+          <t>X &gt; -0.03326</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3390</v>
+        <v>3398</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.01178022806521994</v>
+        <v>0.04270507652146449</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2154544774015221</v>
+        <v>0.265384409593203</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.280991155412039</v>
+        <v>-0.2298337098666465</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.6643859346383536</v>
+        <v>-0.6126494650723799</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.7160091362242937</v>
+        <v>-0.645451927589491</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3143728372981727</v>
+        <v>-0.3273531733692963</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.07192063034175078</v>
+        <v>0.06885324572560592</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1804568731503693</v>
+        <v>0.1483610074869972</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1946823159691036</v>
+        <v>0.1570497090373735</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2744644646491921</v>
+        <v>0.2449858341047388</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2926736241929362</v>
+        <v>0.2761395042157133</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5206123952471486</v>
+        <v>0.5107768298158959</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7069938861523397</v>
+        <v>0.6912639891769956</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.6251654395026165</v>
+        <v>0.6039913974386053</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02379</t>
+          <t>X &gt; -0.02377</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3141</v>
+        <v>3149</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3070029870560944</v>
+        <v>-0.261853433500022</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.04576762661309886</v>
+        <v>0.008706655367362259</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5821116035913221</v>
+        <v>-0.5263171391686896</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5935489681310102</v>
+        <v>-0.5378084672854939</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3841374096013368</v>
+        <v>-0.312466823713045</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.05499717920386615</v>
+        <v>-0.02238541996725729</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4003178744905753</v>
+        <v>0.4418795634783876</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3956205659825116</v>
+        <v>0.4060931826989673</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.5112261282954762</v>
+        <v>0.5137257127721995</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.442140893547851</v>
+        <v>0.4518018938619761</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6370906210184728</v>
+        <v>0.6286138272782722</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.9441070284241917</v>
+        <v>0.9407488186114108</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9877291457913913</v>
+        <v>0.9900353364920349</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8497712101691874</v>
+        <v>0.8762640865645821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.01429</t>
+          <t>X &gt; -0.01427</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2854</v>
+        <v>2862</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3677480249458114</v>
+        <v>-0.3316524313700739</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.05787229474732669</v>
+        <v>-0.04865850557979456</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9928134105195383</v>
+        <v>-0.9467408851032744</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.018654656271323</v>
+        <v>-1.00752666733127</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6991337220563523</v>
+        <v>-0.675362329682919</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5765848672464458</v>
+        <v>-0.5770968806720163</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.177865612648219</v>
+        <v>0.1841731856886284</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3751326331971541</v>
+        <v>0.3661987682162859</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4734804786066888</v>
+        <v>0.4689397462258427</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3778247352951638</v>
+        <v>0.3786074979291953</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5778971397159083</v>
+        <v>0.5586794150455603</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.052346315230224</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.107601035705009</v>
+        <v>1.094898145511323</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8980733077742329</v>
+        <v>0.9098399070029615</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.004788</t>
+          <t>X &gt; -0.004778</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2495</v>
+        <v>2503</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.5240470209496948</v>
+        <v>-0.4782393149268174</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1810608156989417</v>
+        <v>0.1912866180560044</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9111643593320409</v>
+        <v>-0.8586377436525936</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.079270267242869</v>
+        <v>-1.066357057382199</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6766252429305268</v>
+        <v>-0.6564478640165632</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.7391072708724096</v>
+        <v>-0.7428004138329172</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2640415405743965</v>
+        <v>-0.26300508347137</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.09136608200208229</v>
+        <v>-0.1080825493319466</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1496749521988505</v>
+        <v>0.134497557186215</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.2422771642723518</v>
+        <v>0.229199327808935</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.7806915068161615</v>
+        <v>0.7439087205284309</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.15829978993208</v>
+        <v>1.121564275784699</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.281974604343027</v>
+        <v>1.245575678294351</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.21028848795941</v>
+        <v>1.198075435968484</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.004711</t>
+          <t>X &gt; 0.004717</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2064</v>
+        <v>2071</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3091013587196798</v>
+        <v>-0.2461426534033606</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.4445774130813547</v>
+        <v>0.5091207285113768</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3101472891354433</v>
+        <v>-0.2922342271907183</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7334599589677495</v>
+        <v>-0.7633174832885388</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4504934734161097</v>
+        <v>-0.4545001062028859</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.6362112312206278</v>
+        <v>-0.6643400700094446</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.1412114455592643</v>
+        <v>-0.1458455800843268</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.01973923432549185</v>
+        <v>0.01573478694545827</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2270843287092461</v>
+        <v>0.2200749191214086</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4194466781126991</v>
+        <v>0.4097598518199348</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1936907015275224</v>
+        <v>0.1573568560212948</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6426180483184325</v>
+        <v>0.6016239794865754</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.024827090839572</v>
+        <v>0.9786668251235184</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7940101949392613</v>
+        <v>0.7726082081339172</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1651</v>
+        <v>1656</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.05531585352361645</v>
+        <v>0.111949657933998</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8595886976578555</v>
+        <v>0.9127424530452188</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1994338948266545</v>
+        <v>-0.1719997408439653</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.33732469326727</v>
+        <v>-1.337819185645273</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.030203618343648</v>
+        <v>-0.9816576985778767</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.759399637017736</v>
+        <v>-1.735442228068123</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.662950575994046</v>
+        <v>-1.614938897003725</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.344995065191419</v>
+        <v>-1.295747502797703</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.192198159583626</v>
+        <v>-1.151560691644647</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.8607275200681244</v>
+        <v>-0.8280462772905395</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.092531209287756</v>
+        <v>-1.092573198256581</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.4194288355080289</v>
+        <v>-0.4305417265921747</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.1027650343854205</v>
+        <v>0.08009744829327303</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2073619807960796</v>
+        <v>0.2083693634487318</v>
       </c>
     </row>
     <row r="22">
@@ -3046,465 +3046,465 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1066029953408432</v>
+        <v>0.1494626431981203</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7024184243470231</v>
+        <v>0.7356084283602016</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.5294914687793977</v>
+        <v>-0.529644858783719</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.312508334323461</v>
+        <v>-1.313002826701464</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.241969881330874</v>
+        <v>-1.193423961565102</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.39056236615545</v>
+        <v>-2.366604957205837</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.323065723899553</v>
+        <v>-2.275054044909233</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.420271353987651</v>
+        <v>-1.371023791593935</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.9485290051831896</v>
+        <v>-0.8752718954034933</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.223990988076174</v>
+        <v>-1.166375970891231</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.005798660927788</v>
+        <v>-0.9899989146221486</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2427712741396206</v>
+        <v>-0.246900670407932</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2958471821469004</v>
+        <v>0.27118341216066</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.06356756519786444</v>
+        <v>0.06360726960981111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.03321</t>
+          <t>X &gt; 0.0332</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2987528426785602</v>
+        <v>-0.2373845521597104</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.41074417621207</v>
+        <v>1.451734786639626</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4467128294076872</v>
+        <v>0.4465594394033658</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4667052907610625</v>
+        <v>-0.4671997831390655</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.530611542148975</v>
+        <v>-0.4820656223832032</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.466634096954124</v>
+        <v>-1.442676688004511</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.07696115451251</v>
+        <v>-1.02894947552219</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5952631948836853</v>
+        <v>-0.5460156324899685</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.4664920307233444</v>
+        <v>-0.3932349209436481</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.074488858376021</v>
+        <v>-1.027310181075528</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.3714088807181994</v>
+        <v>-0.3775606855376097</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.7627728264627009</v>
+        <v>0.7242493155844016</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.294096759067465</v>
+        <v>1.277857992436125</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.139242494926727</v>
+        <v>1.147396213085273</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.04271</t>
+          <t>X &gt; 0.0427</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1568330902159332</v>
+        <v>0.2936264928700254</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.766045590352576</v>
+        <v>2.748816353115053</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.667874440064132</v>
+        <v>1.601966075881329</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.9774665238635123</v>
+        <v>0.9121779859484676</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4391769707678179</v>
+        <v>0.422928844996548</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0331512348695</v>
+        <v>-0.006861748596691086</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1829074641144572</v>
+        <v>0.1666741996485754</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4192385858611374</v>
+        <v>0.4034175516773999</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.061656194871773</v>
+        <v>1.069021054952785</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7472678929581917</v>
+        <v>0.7135765490792494</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.012050302773126</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.288822104135683</v>
+        <v>2.206947101203134</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.573724129788204</v>
+        <v>2.51436528705149</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.151986219497694</v>
+        <v>3.231794224008311</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.05221</t>
+          <t>X &gt; 0.05219</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>678</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.058906978315214</v>
+        <v>1.09813559779343</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.725007020944595</v>
+        <v>3.785945257851132</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.592772509345892</v>
+        <v>2.59261911934157</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.017982903671722</v>
+        <v>3.017488411293719</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.774678601313489</v>
+        <v>2.823224521079261</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.777067380211115</v>
+        <v>2.801024789160728</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.987342271682408</v>
+        <v>3.035353950672729</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.192839999577082</v>
+        <v>1.242087561970799</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.754276722110355</v>
+        <v>2.827533831890051</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.641821052624152</v>
+        <v>2.741168377918726</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.732105145101421</v>
+        <v>2.832013181120097</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.503946424300409</v>
+        <v>3.627643045328654</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.263736573936846</v>
+        <v>4.412426121714674</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.226935351007043</v>
+        <v>5.398934110573705</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.06171</t>
+          <t>X &gt; 0.06169</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>530</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.9153103845599873</v>
+        <v>0.9738806421563311</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.832426178288607</v>
+        <v>3.91047756829991</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.437654793533568</v>
+        <v>3.437501403529247</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.888634654103065</v>
+        <v>4.888140161725062</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.406948874592274</v>
+        <v>3.455494794358046</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.459039885359438</v>
+        <v>4.482997294309051</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.808291790244212</v>
+        <v>3.856303469234533</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.586506165325396</v>
+        <v>2.635753727719113</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.091561744651678</v>
+        <v>3.164818854431374</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.128435401152011</v>
+        <v>4.227782726446584</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.923734242891818</v>
+        <v>4.023642278910494</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.524150131096192</v>
+        <v>4.647846752124437</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>5.04739550419788</v>
+        <v>5.196085051975707</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.650489644990451</v>
+        <v>5.822488404557113</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.07121</t>
+          <t>X &gt; 0.07118</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>431</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4193159880271367</v>
+        <v>0.3901201936745053</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.448501124661675</v>
+        <v>3.447314338217019</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.517766862876478</v>
+        <v>3.517613472872156</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.808084813889437</v>
+        <v>4.807590321511434</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.877683891884232</v>
+        <v>2.926229811650003</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.335150728943901</v>
+        <v>4.359108137893514</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.858329000768222</v>
+        <v>2.906340679758543</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.391260356981483</v>
+        <v>2.4405079193752</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.330278200458707</v>
+        <v>2.403535310238404</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.728619264917711</v>
+        <v>4.827966590212284</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.291899545172605</v>
+        <v>4.39180758119128</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.79031482049777</v>
+        <v>4.914011441526014</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.45833102054862</v>
+        <v>6.607020568326448</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.684066670775152</v>
+        <v>6.856065430341815</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.08071</t>
+          <t>X &gt; 0.08068</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>353</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3562701381830777</v>
+        <v>-0.385465932535709</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.414980029376331</v>
+        <v>3.413793242931675</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.43663923952213</v>
+        <v>4.436485849517808</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.416722740051007</v>
+        <v>5.416228247673004</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.028574830014797</v>
+        <v>4.077120749780569</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.459093335570572</v>
+        <v>5.483050744520185</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.957952381403551</v>
+        <v>4.005964060393872</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.357739261696139</v>
+        <v>2.406986824089856</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.146615462113864</v>
+        <v>3.219872571893561</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.412843974565874</v>
+        <v>5.512191299860447</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.791712221404836</v>
+        <v>3.891620257423511</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.542804254779988</v>
+        <v>3.666500875808232</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.672228472288111</v>
+        <v>5.820918020065939</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.181250241494801</v>
+        <v>6.353249001061464</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.09021</t>
+          <t>X &gt; 0.09017</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>288</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2968617472434261</v>
+        <v>0.2676659528907948</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.582570936091223</v>
+        <v>5.582417546086901</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.407240524124028</v>
+        <v>6.406746031746025</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.827284304361669</v>
+        <v>4.875830224127441</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.902436111774534</v>
+        <v>7.926393520724147</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.73439241917503</v>
+        <v>5.782404098165351</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.878434886499406</v>
+        <v>3.927682448893123</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.206341618865515</v>
+        <v>5.279598728645212</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.786978378091213</v>
+        <v>6.886325703385786</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.887832775386578</v>
+        <v>5.987740811405253</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.574988705519679</v>
+        <v>5.698685326547924</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.585393407761828</v>
+        <v>7.734082955539655</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.158351280210589</v>
+        <v>8.330350039777251</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.0997</t>
+          <t>X &gt; 0.09967</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.842618158193929</v>
+        <v>-1.66265419776834</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.354706387040125</v>
+        <v>3.533829734024962</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.810998832072308</v>
+        <v>3.987549372828902</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.366755890554288</v>
+        <v>4.541162227602896</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.402934422564975</v>
+        <v>3.628184273091662</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.25349994156177</v>
+        <v>6.443342673266521</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.53522895692241</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.574061364040773</v>
+        <v>3.798209755861102</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.640738781986087</v>
+        <v>5.456152400961606</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.492947645230693</v>
+        <v>6.327239074383904</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.862714572076882</v>
+        <v>5.699369813288492</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.471560809538587</v>
+        <v>5.333807737094062</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.179069530693269</v>
+        <v>7.057293878326846</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.404805180919801</v>
+        <v>7.730067553901534</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>190</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.276318929033401</v>
+        <v>3.275132142588745</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.460494912699403</v>
+        <v>4.460341522695082</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.642857142857139</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.105062082139447</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.507699269669274</v>
+        <v>7.531656678618887</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.844041541982051</v>
+        <v>5.892053220972372</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.421253899567269</v>
+        <v>7.494511009346965</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.202914050605841</v>
+        <v>9.302261375900414</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.471897102871964</v>
+        <v>8.571805138890639</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.506275255227287</v>
+        <v>8.629971876255532</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.665071770334919</v>
+        <v>9.813761318112746</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.36449163108778</v>
+        <v>9.536490390654443</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>157</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.162444692954736</v>
+        <v>-2.191640487307367</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.780509341369971</v>
+        <v>5.779322554925315</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.93350865725187</v>
+        <v>7.933355267247549</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.426791125681</v>
+        <v>7.426296633302996</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.977673547107599</v>
+        <v>5.026219466873371</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.733646302857338</v>
+        <v>9.757603711806951</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.648935943591169</v>
+        <v>9.69694762258149</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.907981949485958</v>
+        <v>7.957229511879675</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.483942468122414</v>
+        <v>8.557199577902111</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.81873704758873</v>
+        <v>10.9180843728833</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.340150539010068</v>
+        <v>9.440058575028743</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.374528691365391</v>
+        <v>9.498225312393636</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.591320513211215</v>
+        <v>9.740010060989043</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.817056163437748</v>
+        <v>9.98905492300441</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>124</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.093819256340801</v>
+        <v>-4.123015050693432</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.585317231240531</v>
+        <v>5.584130444795875</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.609900685195164</v>
+        <v>7.609747295190843</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.127222602977078</v>
+        <v>6.126728110599075</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.395384662784608</v>
+        <v>6.443930582550379</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9.918565144032598</v>
+        <v>9.942522552982211</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.41449994605675</v>
+        <v>7.462511625047071</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.334528076463563</v>
+        <v>5.38377563885728</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.079997532844011</v>
+        <v>6.153254642623708</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.455885188127056</v>
+        <v>8.555232513421629</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>9.05763564277008</v>
+        <v>9.157543678788755</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.285562182222186</v>
+        <v>8.409258803250431</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.671862941811995</v>
+        <v>8.820552489589822</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.704050204941758</v>
+        <v>9.876048964508421</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.561744030247972</v>
+        <v>4.560557243803316</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.97466495318524</v>
+        <v>8.974511563180918</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.143351635235142</v>
+        <v>8.142857142857139</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.566600543677907</v>
+        <v>8.615146463443679</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.71012841946684</v>
+        <v>12.73408582841645</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.66387959866221</v>
+        <v>11.71189127765253</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.350657108721627</v>
+        <v>7.399904671115344</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.251213413737311</v>
+        <v>8.324470523517007</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.2474484635613</v>
+        <v>11.34679578885587</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.00428576683957</v>
+        <v>12.10419380285825</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.07712545765643</v>
+        <v>11.20082207868467</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.61851306588149</v>
+        <v>11.76720261365931</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.80578717764647</v>
+        <v>12.97778593721313</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.1472</t>
+          <t>X &gt; 0.1471</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.859092042338119</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.227412205932488</v>
+        <v>6.227258815928167</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.819347796425156</v>
+        <v>5.867893716190927</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.17486860965123</v>
+        <v>13.22288028864155</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.374466632531153</v>
+        <v>4.42371419492487</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.415946632059473</v>
+        <v>9.515293957354046</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.59219785475166</v>
+        <v>11.69210589077034</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.20642515379357</v>
+        <v>11.3551147015714</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.43216080402011</v>
+        <v>11.60415956358677</v>
       </c>
     </row>
   </sheetData>
@@ -3904,781 +3904,781 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1283</t>
+          <t>X &lt; -0.1282</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.61432206470374</v>
+        <v>10.58512627035111</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.003135971639914</v>
+        <v>9.001949185195258</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.417888396408685</v>
+        <v>7.417735006404364</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.548113539997047</v>
+        <v>7.547619047619044</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.819347796425156</v>
+        <v>5.867893716190927</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>3.183990442054963</v>
+        <v>3.23323800444868</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1078628917500524</v>
+        <v>-0.008515566455479018</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3125640500102449</v>
+        <v>-0.2126560139915696</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.659138278607308</v>
+        <v>-2.535441657579064</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.079289131920717</v>
+        <v>-2.93059958414289</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.1188</t>
+          <t>X &lt; -0.1187</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.879444329826015</v>
+        <v>7.850248535473384</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.07006003856398</v>
+        <v>8.068873252119324</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.774387752908034</v>
+        <v>6.774234362903712</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.102811094694601</v>
+        <v>5.102316602316598</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.861818838896205</v>
+        <v>1.910364758661977</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.147113437775019</v>
+        <v>-4.123156028825406</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.430021995239386</v>
+        <v>-2.382010316249065</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.607413865478385</v>
+        <v>1.656661427872102</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.660775498251603</v>
+        <v>-5.587518388471906</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.907090690977853</v>
+        <v>-2.80774336568328</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.913593651039854</v>
+        <v>-4.813685615021178</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-3.077413696882722</v>
+        <v>-2.953717075854478</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.59666364929523</v>
+        <v>-2.447974101517403</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.3317747036340037</v>
+        <v>0.5037734632006661</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.1093</t>
+          <t>X &lt; -0.1092</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>138</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.939373824538109</v>
+        <v>6.910178030185477</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.704999325677186</v>
+        <v>1.70381253923253</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.5855902597627249</v>
+        <v>0.5854368697584036</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.7334599589677495</v>
+        <v>-0.7339544513457525</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.996387193222873</v>
+        <v>-1.947841273457101</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.771476931703724</v>
+        <v>-6.747519522754111</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-6.131549609810477</v>
+        <v>-6.083537930820157</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.250792166640693</v>
+        <v>-2.201544604246976</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.384238091279407</v>
+        <v>-7.310980981499711</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.4370554383339</v>
+        <v>-2.337708113039326</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.679842212354721</v>
+        <v>-7.556145591326477</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.476804659871028</v>
+        <v>-4.328115112093201</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.077155966166238</v>
+        <v>-1.905157206599576</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.09978</t>
+          <t>X &lt; -0.09973</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>170</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.930848675348003</v>
+        <v>6.901652880995371</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.79025081757829</v>
+        <v>1.789064031133634</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3692264495296911</v>
+        <v>-0.3693798395340124</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2390013059413292</v>
+        <v>-0.2394957983193322</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.365526153154669</v>
+        <v>-1.316980233388897</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-8.12697565293135</v>
+        <v>-8.103018243981737</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.446980129844576</v>
+        <v>-6.398968450854255</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.796401714807779</v>
+        <v>-2.747154152414062</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.622089753683504</v>
+        <v>-4.548832643903808</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7661261970721824</v>
+        <v>-0.6667788717776091</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.735533237685317</v>
+        <v>-2.635625201666642</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.465860967682929</v>
+        <v>-4.342164346654684</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.944835350408106</v>
+        <v>-1.796145802630278</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.719099700181573</v>
+        <v>-1.547100940614911</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.09028</t>
+          <t>X &lt; -0.09024</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>213</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.674013546930432</v>
+        <v>6.644817752577801</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.306958909265667</v>
+        <v>1.305772122821011</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9121875245106281</v>
+        <v>0.9120341345063068</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5729291000238774</v>
+        <v>0.5724346076458744</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.9736066830784083</v>
+        <v>1.02215260284418</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.832305672263026</v>
+        <v>-4.808348263313412</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.978048895378961</v>
+        <v>-3.930037216388641</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2197654264896372</v>
+        <v>-0.1705178640959204</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.158681855312885</v>
+        <v>-2.085424745533189</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7472678929581917</v>
+        <v>0.8466152182527651</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.3964004014522402</v>
+        <v>-0.2964923654335649</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.239956521397382</v>
+        <v>-2.116259900369137</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.7821731024103258</v>
+        <v>-0.6334835546324982</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.434371724484258</v>
+        <v>-2.262372964917596</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.08078</t>
+          <t>X &lt; -0.08074</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>258</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.883425054736968</v>
+        <v>4.854229260384336</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.334254465549101</v>
+        <v>1.333067679104445</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.102273778468486</v>
+        <v>2.102120388464165</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.457305123607235</v>
+        <v>1.456810631229231</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.469403167410768</v>
+        <v>2.51794908717654</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.209966989000662</v>
+        <v>-4.186009580051049</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.744289751367603</v>
+        <v>-2.696278072377282</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.052207496318523</v>
+        <v>1.10145505871224</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.17156535787867</v>
+        <v>-0.09830824809897365</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9165003419155013</v>
+        <v>1.015847667210075</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.06339461479430497</v>
+        <v>0.03651342122437029</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.129791656237423</v>
+        <v>-3.006095035209178</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.387151811876421</v>
+        <v>-2.238462264098594</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.099400657773913</v>
+        <v>-3.92740189820725</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.07128</t>
+          <t>X &lt; -0.07125</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>325</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.134468584850261</v>
+        <v>4.105272790497629</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.907897876401826</v>
+        <v>1.90671108995717</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.4362034147237</v>
+        <v>2.436050024719378</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.181813173696682</v>
+        <v>3.181318681318679</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.951215928293294</v>
+        <v>2.999761848059066</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.212948503610079</v>
+        <v>-3.188991094660466</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.451505016722408</v>
+        <v>-1.403493337732087</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5429648010293207</v>
+        <v>0.5922123634230374</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.056478893954996</v>
+        <v>-0.9832217841752993</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3679361518233151</v>
+        <v>-0.2685888265287417</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.188021925468121</v>
+        <v>-1.088113889449446</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.999797619266651</v>
+        <v>-2.876100998238407</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.80456385719544</v>
+        <v>-2.655874309417612</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.809597437738134</v>
+        <v>-3.637598678171472</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.06178</t>
+          <t>X &lt; -0.06175</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.544209597606347</v>
+        <v>2.489888175113023</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.184279785949556</v>
+        <v>1.156711089957163</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2869958383804558</v>
+        <v>0.01297310164246568</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.673502389003993</v>
+        <v>1.642857142857146</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.8839565545012533</v>
+        <v>0.6536080019052264</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.587513636969184</v>
+        <v>-2.573606479275853</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.918455152014253</v>
+        <v>-1.884262568501313</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.380498670172848</v>
+        <v>-1.350095328884656</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.195249670916724</v>
+        <v>-2.137067938021453</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.040143341618453</v>
+        <v>-1.960896518836435</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.496100781285676</v>
+        <v>-2.530951753339949</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.220516598779597</v>
+        <v>-4.22717098088733</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.389411170685968</v>
+        <v>-4.371702341035125</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-5.41995692749461</v>
+        <v>-5.375790311099948</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.05228</t>
+          <t>X &lt; -0.05225</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>494</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.579812714404916</v>
+        <v>2.641403326628165</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9686266213410875</v>
+        <v>1.058226241472312</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.383571835776337</v>
+        <v>1.270548859218223</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.133230177745261</v>
+        <v>3.218614718614717</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.582794875661712</v>
+        <v>1.517244365541579</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.751410042071619</v>
+        <v>-0.6342125398819078</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.6336912515402133</v>
+        <v>-0.4928484270871678</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.08861414633910414</v>
+        <v>0.05141982263049272</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.161742051849728</v>
+        <v>-0.9956537966073071</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.404373398786873</v>
+        <v>-1.213421771361688</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.013932856642214</v>
+        <v>-1.914024820623538</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.991700453274746</v>
+        <v>-2.868003832246501</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.816709606183288</v>
+        <v>-3.66802005840546</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.19826140534947</v>
+        <v>-4.026262645782808</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.04279</t>
+          <t>X &lt; -0.04276</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.928401773126211</v>
+        <v>1.884581375776364</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.149162435470032</v>
+        <v>1.130591686972089</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.251895210448779</v>
+        <v>2.229391012090218</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.214067109444798</v>
+        <v>3.354299928926793</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.675777556349104</v>
+        <v>2.699213308704557</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8100900219242817</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.151059085841702</v>
+        <v>1.08713046632456</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.683990442054963</v>
+        <v>0.6212977059412168</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1230082855321868</v>
+        <v>0.08681265899347324</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3935771774643442</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.0982783357245367</v>
+        <v>-0.1849705211898041</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.897233516702542</v>
+        <v>-1.787933351931223</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.817384370015951</v>
+        <v>-2.681430148926943</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.424982053122754</v>
+        <v>-2.266272330100939</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03329</t>
+          <t>X &lt; -0.03326</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1239124319815303</v>
+        <v>-0.1111219258970806</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.7248848427849666</v>
+        <v>-0.9367232534771759</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.294575030401546</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.949577810584572</v>
+        <v>2.713564213564212</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.173677075786209</v>
+        <v>2.85562820392542</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.438014256628406</v>
+        <v>1.486999581330203</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1021215757359144</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5691902195226533</v>
+        <v>-0.4283781571674865</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6301723760454294</v>
+        <v>-0.4653507663042831</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9711853199579821</v>
+        <v>-0.8407953810361875</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.048660015113846</v>
+        <v>-0.975163548651004</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.03209356759313</v>
+        <v>-1.987732079451234</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.833923810219517</v>
+        <v>-2.763118142897191</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.480961696888656</v>
+        <v>-2.387330568587778</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02379</t>
+          <t>X &lt; -0.02377</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9872920619511945</v>
+        <v>0.8488133190669558</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2955545784268949</v>
+        <v>0.1293598423563935</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.829423502254301</v>
+        <v>1.655007650586803</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.863216630413547</v>
+        <v>1.688922401974224</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.228495061888722</v>
+        <v>1.007734681367786</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2286909380293594</v>
+        <v>0.1288887222596529</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.059085841694525</v>
+        <v>-1.179368134720129</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.043062698041659</v>
+        <v>-1.069385156139937</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.393899927028201</v>
+        <v>-1.39426563475849</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.18101679099091</v>
+        <v>-1.205853291170733</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.772191379202795</v>
+        <v>-1.741960043295606</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.703996801726703</v>
+        <v>-2.690123357015331</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.834292582576339</v>
+        <v>-2.841141835725601</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.415320217373967</v>
+        <v>-2.495757860030082</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.01429</t>
+          <t>X &lt; -0.01427</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8373343465395564</v>
+        <v>0.7581075590348831</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.247520517911255</v>
+        <v>0.2267711951412394</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.192371774665645</v>
+        <v>2.086977609531267</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.247125220140802</v>
+        <v>2.216861650745948</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.557892270818698</v>
+        <v>1.502218069523551</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.293674782469402</v>
+        <v>1.291055174859487</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2605055400086371</v>
+        <v>-0.2733603128622164</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.6864079442284492</v>
+        <v>-0.6640051033207541</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.8986760311596953</v>
+        <v>-0.8857511584879632</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6895933146302582</v>
+        <v>-0.6898121814870422</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.121223368503159</v>
+        <v>-1.078375323569212</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.14584672900714</v>
+        <v>-2.109886820259518</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.263425721503602</v>
+        <v>-2.237877212175228</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.810761175664361</v>
+        <v>-1.837888953933451</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.004788</t>
+          <t>X &lt; -0.004778</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.812852515459717</v>
+        <v>0.7443260449355051</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1728622186100566</v>
+        <v>-0.1879634662558587</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.39198634912897</v>
+        <v>1.311789669689794</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.640976338323028</v>
+        <v>1.619188503803876</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.043304362424479</v>
+        <v>1.011596167585694</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.136244786759676</v>
+        <v>1.139833425993537</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4901395456118109</v>
+        <v>0.4871110253411999</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2343572871868247</v>
+        <v>0.2581047895286019</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1240668681461798</v>
+        <v>-0.101522914324768</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2601248673314771</v>
+        <v>-0.2406831222744898</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.059710023212141</v>
+        <v>-1.004894617618078</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.620215868477281</v>
+        <v>-1.566810881826619</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.802413122742507</v>
+        <v>-1.751434331343425</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.695654272040059</v>
+        <v>-1.680536737736617</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.004711</t>
+          <t>X &lt; 0.004717</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2112</v>
+        <v>2116</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3296649803300795</v>
+        <v>0.2676659528907948</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3586427663203011</v>
+        <v>-0.4209725258620409</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3335423706637926</v>
+        <v>0.3152329886481056</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7473213894884552</v>
+        <v>0.7746838848533741</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4714923421867283</v>
+        <v>0.4737586610389215</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6531456671198441</v>
+        <v>0.6783954048503844</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2159746876716397</v>
+        <v>0.2196488358342208</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.05899044205496295</v>
+        <v>0.06256379417050084</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1440371690132736</v>
+        <v>-0.1370679380214455</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3310771774643442</v>
+        <v>-0.3214439468685271</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.1096419720881698</v>
+        <v>-0.0743854082988662</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5487486682176979</v>
+        <v>-0.5093265351011595</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9215510366826223</v>
+        <v>-0.8782096300516073</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.6958153864560899</v>
+        <v>-0.6764237472422963</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2525</v>
+        <v>2531</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.01348610554422436</v>
+        <v>-0.05045027431633997</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4981052831558443</v>
+        <v>-0.5316989848165434</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1555603122710423</v>
+        <v>0.1371368167152625</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9002686312825787</v>
+        <v>0.8966942148760211</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.7001589583751056</v>
+        <v>0.6654190255272709</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.177752567470733</v>
+        <v>1.156996120172742</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.154686575618769</v>
+        <v>1.118298503208692</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9472525164809369</v>
+        <v>0.9109413285847907</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.8466820780895858</v>
+        <v>0.817190737057409</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6301757916567965</v>
+        <v>0.6071508184416672</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7817691702137068</v>
+        <v>0.780503680825575</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.3410879401462239</v>
+        <v>0.3479264547665437</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.0001136505699506074</v>
+        <v>0.01455952215365386</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.06854640955840097</v>
+        <v>-0.06965654523527576</v>
       </c>
     </row>
     <row r="22">
@@ -4740,465 +4740,465 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2866</v>
+        <v>2873</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.02874211749087863</v>
+        <v>-0.04825329506729048</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2646838911695113</v>
+        <v>-0.2791418920123263</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2642577133662414</v>
+        <v>0.2633198422804597</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6224602703326383</v>
+        <v>0.6203111837867255</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5909554990673485</v>
+        <v>0.5665157048892553</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.11672182606025</v>
+        <v>1.101506328776907</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.121141576837402</v>
+        <v>1.094904098165351</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7083976944956873</v>
+        <v>0.683162746836075</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4925002050764249</v>
+        <v>0.4570946749041909</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6192120330925732</v>
+        <v>0.5910673323974862</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5191498702980155</v>
+        <v>0.5109018375217715</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.1698517059459803</v>
+        <v>0.1713906405575898</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.07590082159134681</v>
+        <v>-0.06500658285051486</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.03000747932664893</v>
+        <v>0.02964810219747704</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.03321</t>
+          <t>X &lt; 0.0332</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3125</v>
+        <v>3133</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1187649901993026</v>
+        <v>0.09803066875169009</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4226700878611069</v>
+        <v>-0.4355280957934724</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1300270353241757</v>
+        <v>-0.1295205370343808</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.17719582425174</v>
+        <v>0.176741966274264</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1992811814687343</v>
+        <v>0.1822521775895041</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.5142571980365176</v>
+        <v>0.5043941574640343</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4152009842117863</v>
+        <v>0.3975845652566505</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2534704079543602</v>
+        <v>0.2359989686623365</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2102058124482937</v>
+        <v>0.1847931199772717</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.4156116083793862</v>
+        <v>0.398682696974852</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1789309170203808</v>
+        <v>0.1806262989335963</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2024248609089199</v>
+        <v>-0.1898048382580342</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3807241013019436</v>
+        <v>-0.375672061123467</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3289820531227505</v>
+        <v>-0.3321406507217475</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.04271</t>
+          <t>X &lt; 0.0427</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3325</v>
+        <v>3333</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.02288245739286765</v>
+        <v>-0.05795871483913118</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6588187652773456</v>
+        <v>-0.6542936947318339</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.407689345185851</v>
+        <v>-0.3901369462044286</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.2312358235107297</v>
+        <v>-0.2141575146361276</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.09301714955323348</v>
+        <v>-0.0887618365148839</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.01066186980516193</v>
+        <v>0.02082632527368133</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.00241043719304912</v>
+        <v>0.006455994372934981</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.05772378644208942</v>
+        <v>-0.05367424472771631</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2223442785703753</v>
+        <v>-0.2239463083030557</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1407726902848552</v>
+        <v>-0.1323079662442836</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2084376383996229</v>
+        <v>-0.1998091486267271</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5347447881182319</v>
+        <v>-0.5146663309566577</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6074224538002824</v>
+        <v>-0.5932099192187295</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.7558091207919304</v>
+        <v>-0.7774357388006123</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.05221</t>
+          <t>X &lt; 0.05219</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3498</v>
+        <v>3509</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1881219547724555</v>
+        <v>-0.1954284962871498</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6732987047947603</v>
+        <v>-0.6841980009519304</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.48288376768636</v>
+        <v>-0.4813450801757284</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5653142712642918</v>
+        <v>-0.563451467543544</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5179775528762391</v>
+        <v>-0.5257552726826162</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5188416976949526</v>
+        <v>-0.5218578298587317</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5310616939966266</v>
+        <v>-0.538699428569565</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1835894666208375</v>
+        <v>-0.1925562108192267</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4858032093769395</v>
+        <v>-0.4984794348911166</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.463442016603878</v>
+        <v>-0.48124949350197</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.4808833057331086</v>
+        <v>-0.4987499504271966</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6305668500358692</v>
+        <v>-0.6525837009529454</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7776111014630303</v>
+        <v>-0.8040224575657646</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.9647190456899324</v>
+        <v>-0.9950750575914356</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.06171</t>
+          <t>X &lt; 0.06169</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3646</v>
+        <v>3657</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1168821414936332</v>
+        <v>-0.1252658178005888</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.510910215451652</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4808576483586933</v>
+        <v>-0.4793933105712753</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.6914404873031543</v>
+        <v>-0.6892944797226264</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4763332666977576</v>
+        <v>-0.4819621017499927</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6293099199714973</v>
+        <v>-0.6309052514450144</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5076232756876422</v>
+        <v>-0.5130835291999958</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3300657828446347</v>
+        <v>-0.3362405650298896</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4034228292308981</v>
+        <v>-0.412873508747829</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.5533945290625155</v>
+        <v>-0.5661956174433769</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5236460163676355</v>
+        <v>-0.5366216658260754</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.611049306176227</v>
+        <v>-0.6272309833120886</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.6869118355127029</v>
+        <v>-0.7065114797923471</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.774954625805151</v>
+        <v>-0.7976920712427145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.07121</t>
+          <t>X &lt; 0.07118</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3745</v>
+        <v>3756</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.03280533335500024</v>
+        <v>-0.02934769647095692</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3524162039814627</v>
+        <v>-0.3512506934823278</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3867670120805968</v>
+        <v>-0.3856199432208314</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.5350771264159917</v>
+        <v>-0.5334572490706364</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3131584825915041</v>
+        <v>-0.3178395412554735</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4808572535332161</v>
+        <v>-0.4822143432503481</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2846196632698934</v>
+        <v>-0.2893250186740488</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2306545415049825</v>
+        <v>-0.2356615170824199</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2236583811344843</v>
+        <v>-0.2314577279709411</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4987607819810975</v>
+        <v>-0.5087688592619699</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.4485095701606738</v>
+        <v>-0.4587320980564868</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.5059871863048855</v>
+        <v>-0.5187914637069397</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.6977011523615673</v>
+        <v>-0.7128346501149778</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7240474736834983</v>
+        <v>-0.7418011849298907</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.08071</t>
+          <t>X &lt; 0.08068</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3823</v>
+        <v>3834</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.04775967332383146</v>
+        <v>0.05032487903815763</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2720238967402864</v>
+        <v>-0.2711360239273901</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3919334979202489</v>
+        <v>-0.3907980296969384</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4823984299879172</v>
+        <v>-0.4809722015757458</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3542281057519929</v>
+        <v>-0.3577112799058639</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4863657676303177</v>
+        <v>-0.48719315288335</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.321960931564746</v>
+        <v>-0.3254888116671495</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1741535468020103</v>
+        <v>-0.178220328884656</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2468976705806654</v>
+        <v>-0.2529835410430721</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4553313800599312</v>
+        <v>-0.463241490175669</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3057186563378878</v>
+        <v>-0.3141117643918108</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.282854431735224</v>
+        <v>-0.2935229923027336</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.4791695861944731</v>
+        <v>-0.4915979078530768</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5264730287963033</v>
+        <v>-0.5409332153088258</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.09021</t>
+          <t>X &lt; 0.09017</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3888</v>
+        <v>3899</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.007191344556403578</v>
+        <v>-0.004999350449352846</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2715893030853564</v>
+        <v>-0.2707371330037205</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3960809974529909</v>
+        <v>-0.394955287104338</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4572127567607467</v>
+        <v>-0.4558893396191976</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3401521852457208</v>
+        <v>-0.3428096030077796</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.567789760915403</v>
+        <v>-0.5679755604122718</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3818891383773888</v>
+        <v>-0.3843905766938391</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2443608676522828</v>
+        <v>-0.2473424479627582</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3426137711507522</v>
+        <v>-0.3471089216280134</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.4590105450559818</v>
+        <v>-0.4651240361308311</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3924186595487456</v>
+        <v>-0.3987632605806226</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3693843307556719</v>
+        <v>-0.3775700495664651</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.5180357799756692</v>
+        <v>-0.5276691812124881</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.560784522258551</v>
+        <v>-0.5720394618043656</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.0997</t>
+          <t>X &lt; 0.09967</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3941</v>
+        <v>3951</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1240409750296365</v>
+        <v>0.1135006877265425</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.158380899211636</v>
+        <v>-0.169493805324187</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2105577188795351</v>
+        <v>-0.2215044349552144</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2437655502875131</v>
+        <v>-0.2546434882966153</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1860771583668779</v>
+        <v>-0.1999273516301372</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3559837413528371</v>
+        <v>-0.3679990026403459</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2749794146648838</v>
+        <v>-0.2886334628924203</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1708782345770885</v>
+        <v>-0.1847554249170003</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2939540391848325</v>
+        <v>-0.2836806781630088</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3441475196696686</v>
+        <v>-0.3351063797719576</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.3065271524926203</v>
+        <v>-0.2975609926750025</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2833185619303791</v>
+        <v>-0.2758558095793475</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.3848628073574005</v>
+        <v>-0.37854637419494</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3985928118134368</v>
+        <v>-0.4190172090205309</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3986</v>
+        <v>3997</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1322372577877289</v>
+        <v>0.1332796963100193</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1151136293510575</v>
+        <v>-0.1147406436422429</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1961554698243262</v>
+        <v>-0.1956097326888795</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2525442606607555</v>
+        <v>-0.2518271596135406</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.226602498586459</v>
+        <v>-0.228319107430778</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3411793113601647</v>
+        <v>-0.3413967414481363</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2369950088239676</v>
+        <v>-0.238658172896919</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1894230515990145</v>
+        <v>-0.1912769426743139</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.311803374035172</v>
+        <v>-0.3144792323742749</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.3960834431285036</v>
+        <v>-0.3997867962670796</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.3612097303932131</v>
+        <v>-0.3650369663725215</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3629640416106028</v>
+        <v>-0.3679354953242111</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4179612448591925</v>
+        <v>-0.4239891360617065</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.403908294969213</v>
+        <v>-0.4111018824978032</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4019</v>
+        <v>4030</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.09844904883073013</v>
+        <v>0.09933660449713955</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.184883071253843</v>
+        <v>-0.1843329476479809</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2933251212564372</v>
+        <v>-0.2925205880383146</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.273749382387102</v>
+        <v>-0.2729844413012756</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.177956785785085</v>
+        <v>-0.1793952167132531</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3636428551983997</v>
+        <v>-0.3636015263288499</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.335528097466792</v>
+        <v>-0.3365167176219472</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2673553136386175</v>
+        <v>-0.2685789760600699</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2898479106242107</v>
+        <v>-0.2919626096447416</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3804029293907689</v>
+        <v>-0.3833060379241928</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3226277472942414</v>
+        <v>-0.325711402276319</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3240759273798162</v>
+        <v>-0.3281003877377984</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.3323097431502831</v>
+        <v>-0.3373047618726233</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3413791668326382</v>
+        <v>-0.3472760975263185</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4052</v>
+        <v>4063</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1390101687276371</v>
+        <v>0.1395447011189006</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1304879503698331</v>
+        <v>-0.1300987259937543</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2166298460347349</v>
+        <v>-0.2160401531439931</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1715178871676173</v>
+        <v>-0.1710392480095422</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1793506240905458</v>
+        <v>-0.1803802102755228</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2872190606392593</v>
+        <v>-0.2871903652989403</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1860929220420147</v>
+        <v>-0.1870881213268589</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1222359420422876</v>
+        <v>-0.1234425886536457</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1450058464208226</v>
+        <v>-0.1469007797126949</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2170485778588116</v>
+        <v>-0.2195638411870675</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2353519074466917</v>
+        <v>-0.2378357858511251</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2118199334103252</v>
+        <v>-0.2151113114184611</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2233799288612559</v>
+        <v>-0.2274218563588519</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2551893581573026</v>
+        <v>-0.2598747530687646</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4072</v>
+        <v>4083</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.07722350434936942</v>
+        <v>0.07777880011301619</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.07643121272649012</v>
+        <v>-0.07619489294881987</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2130552374739594</v>
+        <v>-0.2124787791587153</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.192023181031395</v>
+        <v>-0.1914941886845156</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.202460583873787</v>
+        <v>-0.2031857419853011</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3083482019509631</v>
+        <v>-0.3081457117373532</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2571700552876592</v>
+        <v>-0.2577344511419</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.146890708835997</v>
+        <v>-0.1477842503813562</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1698541132904836</v>
+        <v>-0.1713145133639173</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2457198009514201</v>
+        <v>-0.2476594256140245</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2649450023911939</v>
+        <v>-0.2668480285360104</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2413670464030844</v>
+        <v>-0.2439571323124099</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2549406348494117</v>
+        <v>-0.2581496051307184</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2854928586237406</v>
+        <v>-0.2892311505240031</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.1472</t>
+          <t>X &lt; 0.1471</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4092</v>
+        <v>4102</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1378415821331274</v>
+        <v>0.1508845299125312</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.001465127863809812</v>
+        <v>0.01463525135726229</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1120258359184163</v>
+        <v>-0.09850270676989226</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.06605840864589396</v>
+        <v>-0.05266814897166228</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1034236530470949</v>
+        <v>-0.09085806474522684</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2317102296888791</v>
+        <v>-0.2183753357235432</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.229968807140331</v>
+        <v>-0.2171294460871067</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.04929408698359339</v>
+        <v>-0.036804189644144</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1212354700613361</v>
+        <v>-0.109066964074529</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1520407191310085</v>
+        <v>-0.1401463970634254</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1965689340151329</v>
+        <v>-0.1845253951179586</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1729215153998283</v>
+        <v>-0.1614511256937874</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1884650769139</v>
+        <v>-0.1773876486253272</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1933104988705594</v>
+        <v>-0.1827736397286941</v>
       </c>
     </row>
   </sheetData>
